--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="88">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>30/04/2025</t>
+    <t>24/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -98,7 +98,7 @@
     <t>FNY9FG3</t>
   </si>
   <si>
-    <t>fdsfsd</t>
+    <t>dasdsad</t>
   </si>
   <si>
     <t>Cargador Laptop</t>
@@ -120,9 +120,6 @@
   </si>
   <si>
     <t>1446MG00C698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teclado </t>
   </si>
   <si>
     <t>MK235</t>
@@ -1168,17 +1165,17 @@
         <v>4</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C22" s="38" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
@@ -1189,17 +1186,17 @@
         <v>5</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" s="38" t="s">
         <v>31</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1210,17 +1207,17 @@
         <v>6</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1231,17 +1228,17 @@
         <v>7</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1252,17 +1249,17 @@
         <v>8</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
@@ -1273,17 +1270,17 @@
         <v>9</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C27" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="38" t="s">
         <v>49</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>50</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
@@ -1294,17 +1291,17 @@
         <v>10</v>
       </c>
       <c r="B28" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="D28" s="38" t="s">
         <v>53</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>54</v>
       </c>
       <c r="E28" s="38"/>
       <c r="F28" s="38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1315,13 +1312,13 @@
         <v>11</v>
       </c>
       <c r="B29" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="D29" s="38" t="s">
         <v>57</v>
-      </c>
-      <c r="D29" s="38" t="s">
-        <v>58</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38"/>
@@ -1334,17 +1331,17 @@
         <v>12</v>
       </c>
       <c r="B30" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="38" t="s">
         <v>59</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>60</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="38"/>
@@ -1355,17 +1352,17 @@
         <v>13</v>
       </c>
       <c r="B31" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="38" t="s">
+      <c r="D31" s="38" t="s">
         <v>63</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>64</v>
       </c>
       <c r="E31" s="38"/>
       <c r="F31" s="38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
@@ -1376,17 +1373,17 @@
         <v>14</v>
       </c>
       <c r="B32" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="C32" s="38" t="s">
+      <c r="D32" s="38" t="s">
         <v>67</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>68</v>
       </c>
       <c r="E32" s="38"/>
       <c r="F32" s="38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G32" s="38"/>
       <c r="H32" s="38"/>
@@ -1397,17 +1394,17 @@
         <v>15</v>
       </c>
       <c r="B33" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" s="38" t="s">
         <v>70</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>71</v>
       </c>
       <c r="E33" s="38"/>
       <c r="F33" s="38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G33" s="38"/>
       <c r="H33" s="38"/>
@@ -1428,7 +1425,7 @@
       </c>
       <c r="E34" s="38"/>
       <c r="F34" s="38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G34" s="38"/>
       <c r="H34" s="38"/>
@@ -1439,7 +1436,7 @@
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
       <c r="D35" s="22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="22"/>
@@ -1458,11 +1455,11 @@
         <v>23</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E36" s="38"/>
       <c r="F36" s="38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G36" s="38"/>
       <c r="H36" s="38"/>
@@ -1492,7 +1489,7 @@
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B39" s="26"/>
       <c r="C39" s="26"/>
@@ -1516,7 +1513,7 @@
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B41" s="28"/>
       <c r="C41" s="28"/>
@@ -1529,7 +1526,7 @@
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B42" s="28"/>
       <c r="C42" s="28"/>
@@ -1542,7 +1539,7 @@
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B43" s="28"/>
       <c r="C43" s="28"/>
@@ -1555,7 +1552,7 @@
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="24.05">
       <c r="A44" s="29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B44" s="29"/>
       <c r="C44" s="29"/>
@@ -1569,7 +1566,7 @@
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="27">
       <c r="A45" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B45" s="28"/>
       <c r="C45" s="28"/>
@@ -1593,7 +1590,7 @@
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="39">
       <c r="A47" s="31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B47" s="31"/>
       <c r="C47" s="31"/>
@@ -1629,14 +1626,14 @@
     <row r="50" spans="1:10" customHeight="1" ht="15">
       <c r="A50" s="32"/>
       <c r="B50" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C50" s="34"/>
       <c r="D50" s="34"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H50" s="35"/>
       <c r="I50" s="35"/>
@@ -1646,7 +1643,7 @@
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -1679,7 +1676,7 @@
     <row r="54" spans="1:10" customHeight="1" ht="15">
       <c r="A54" s="2"/>
       <c r="B54" s="34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C54" s="34"/>
       <c r="D54" s="34"/>
@@ -1695,7 +1692,7 @@
     <row r="55" spans="1:10" customHeight="1" ht="15">
       <c r="A55" s="2"/>
       <c r="B55" s="34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C55" s="34"/>
       <c r="D55" s="34"/>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>24/04/2025</t>
+    <t>25/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -86,166 +86,16 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t>Laptop</t>
-  </si>
-  <si>
-    <t>DELL</t>
-  </si>
-  <si>
-    <t>Latitude 5520</t>
-  </si>
-  <si>
-    <t>FNY9FG3</t>
-  </si>
-  <si>
-    <t>dasdsad</t>
-  </si>
-  <si>
-    <t>Cargador Laptop</t>
-  </si>
-  <si>
-    <t>LA65NM190</t>
-  </si>
-  <si>
-    <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
-  </si>
-  <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>Logitech</t>
-  </si>
-  <si>
-    <t>K120</t>
-  </si>
-  <si>
-    <t>1446MG00C698</t>
-  </si>
-  <si>
-    <t>MK235</t>
-  </si>
-  <si>
-    <t>2134MR38A788</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>M170</t>
-  </si>
-  <si>
-    <t>2131LZD121R8</t>
-  </si>
-  <si>
-    <t>Docking Station</t>
-  </si>
-  <si>
-    <t>WD19S</t>
-  </si>
-  <si>
-    <t>F9WQSB3</t>
-  </si>
-  <si>
-    <t>Cargador de Doking</t>
-  </si>
-  <si>
-    <t>HA180MP180</t>
-  </si>
-  <si>
-    <t>CN-03XYY8-CH200-17G-0BXA-A04</t>
-  </si>
-  <si>
     <t>Monitor</t>
   </si>
   <si>
+    <t>Dell</t>
+  </si>
+  <si>
     <t>E2724HS</t>
   </si>
   <si>
     <t>CN04XFCWTV2003AH0WDT</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>EliteDysplay E231</t>
-  </si>
-  <si>
-    <t>6CM4083FX3</t>
-  </si>
-  <si>
-    <t>Telefono</t>
-  </si>
-  <si>
-    <t>Polycom</t>
-  </si>
-  <si>
-    <t>VVX 150</t>
-  </si>
-  <si>
-    <t>64167F786244</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>KOBLENZ</t>
-  </si>
-  <si>
-    <t>5216 R</t>
-  </si>
-  <si>
-    <t>Unidad DVD</t>
-  </si>
-  <si>
-    <t>GP60NB50</t>
-  </si>
-  <si>
-    <t>CNH4306278</t>
-  </si>
-  <si>
-    <t>Audifonos</t>
-  </si>
-  <si>
-    <t>Poly</t>
-  </si>
-  <si>
-    <t>Voyager 5200</t>
-  </si>
-  <si>
-    <t>2X492H</t>
-  </si>
-  <si>
-    <t>Diadema</t>
-  </si>
-  <si>
-    <t>POLY</t>
-  </si>
-  <si>
-    <t>108DB1</t>
-  </si>
-  <si>
-    <t>2032CW</t>
-  </si>
-  <si>
-    <t>Cargador de Laptop</t>
-  </si>
-  <si>
-    <t>HSTNN-DA40</t>
-  </si>
-  <si>
-    <t>WDWRT0AAR6Z19W</t>
-  </si>
-  <si>
-    <t>64W9FG3</t>
-  </si>
-  <si>
-    <t>DVZ-VH-TI-00008</t>
-  </si>
-  <si>
-    <t>DA65NM190</t>
-  </si>
-  <si>
-    <t>CN-0FTTTJ-DES00-14U-C63H-A01</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -1113,630 +963,294 @@
         <v>25</v>
       </c>
       <c r="G19" s="38"/>
-      <c r="H19" s="38" t="s">
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+    </row>
+    <row r="20" spans="1:10" customHeight="1" ht="15">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22">
+        <v>123</v>
+      </c>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+    </row>
+    <row r="21" spans="1:10" customHeight="1" ht="15">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+    </row>
+    <row r="22" spans="1:10" customHeight="1" ht="15">
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+    </row>
+    <row r="23" spans="1:10" customHeight="1" ht="15">
+      <c r="A23" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="I19" s="38"/>
-    </row>
-    <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="38">
-        <v>2</v>
-      </c>
-      <c r="B20" s="38" t="s">
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+    </row>
+    <row r="24" spans="1:10" customHeight="1" ht="15">
+      <c r="A24" s="27"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+    </row>
+    <row r="25" spans="1:10" customHeight="1" ht="15">
+      <c r="A25" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="38" t="s">
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+    </row>
+    <row r="26" spans="1:10" customHeight="1" ht="15">
+      <c r="A26" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38" t="s">
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+    </row>
+    <row r="27" spans="1:10" customHeight="1" ht="15">
+      <c r="A27" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-    </row>
-    <row r="21" spans="1:10" customHeight="1" ht="15">
-      <c r="A21" s="38">
-        <v>3</v>
-      </c>
-      <c r="B21" s="38" t="s">
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+    </row>
+    <row r="28" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A28" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" customHeight="1" ht="27">
+      <c r="A29" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+    </row>
+    <row r="30" spans="1:10" customHeight="1" ht="15">
+      <c r="A30" s="30"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+    </row>
+    <row r="31" spans="1:10" customHeight="1" ht="39">
+      <c r="A31" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38" t="s">
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+    </row>
+    <row r="32" spans="1:10" customHeight="1" ht="15">
+      <c r="A32" s="32"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+    </row>
+    <row r="33" spans="1:10" customHeight="1" ht="15">
+      <c r="A33" s="2"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="15">
+      <c r="A34" s="32"/>
+      <c r="B34" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-    </row>
-    <row r="22" spans="1:10" customHeight="1" ht="15">
-      <c r="A22" s="38">
-        <v>4</v>
-      </c>
-      <c r="B22" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="38" t="s">
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38" t="s">
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+    </row>
+    <row r="35" spans="1:10" customHeight="1" ht="15">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-    </row>
-    <row r="23" spans="1:10" customHeight="1" ht="15">
-      <c r="A23" s="38">
-        <v>5</v>
-      </c>
-      <c r="B23" s="38" t="s">
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+    </row>
+    <row r="36" spans="1:10" customHeight="1" ht="15">
+      <c r="A36" s="2"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
+      <c r="I36" s="37"/>
+    </row>
+    <row r="37" spans="1:10" customHeight="1" ht="15">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" spans="1:10" customHeight="1" ht="15">
+      <c r="A38" s="2"/>
+      <c r="B38" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-    </row>
-    <row r="24" spans="1:10" customHeight="1" ht="15">
-      <c r="A24" s="38">
-        <v>6</v>
-      </c>
-      <c r="B24" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-    </row>
-    <row r="25" spans="1:10" customHeight="1" ht="15">
-      <c r="A25" s="38">
-        <v>7</v>
-      </c>
-      <c r="B25" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-    </row>
-    <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="38">
-        <v>8</v>
-      </c>
-      <c r="B26" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-    </row>
-    <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="38">
-        <v>9</v>
-      </c>
-      <c r="B27" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="38"/>
-    </row>
-    <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="38">
-        <v>10</v>
-      </c>
-      <c r="B28" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-    </row>
-    <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="38">
-        <v>11</v>
-      </c>
-      <c r="B29" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
-    </row>
-    <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="38">
-        <v>12</v>
-      </c>
-      <c r="B30" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-    </row>
-    <row r="31" spans="1:10" customHeight="1" ht="15">
-      <c r="A31" s="38">
-        <v>13</v>
-      </c>
-      <c r="B31" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
-    </row>
-    <row r="32" spans="1:10" customHeight="1" ht="15">
-      <c r="A32" s="38">
-        <v>14</v>
-      </c>
-      <c r="B32" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="38"/>
-    </row>
-    <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="38">
-        <v>15</v>
-      </c>
-      <c r="B33" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="38">
-        <v>16</v>
-      </c>
-      <c r="B34" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D34" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="38"/>
-    </row>
-    <row r="35" spans="1:10" customHeight="1" ht="15">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-    </row>
-    <row r="36" spans="1:10" customHeight="1" ht="15">
-      <c r="A36" s="38">
-        <v>17</v>
-      </c>
-      <c r="B36" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D36" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-    </row>
-    <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="16"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-    </row>
-    <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="25"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
-    </row>
-    <row r="39" spans="1:10" customHeight="1" ht="15">
-      <c r="A39" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-    </row>
-    <row r="40" spans="1:10" customHeight="1" ht="15">
-      <c r="A40" s="27"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-    </row>
-    <row r="41" spans="1:10" customHeight="1" ht="15">
-      <c r="A41" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-    </row>
-    <row r="42" spans="1:10" customHeight="1" ht="15">
-      <c r="A42" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-    </row>
-    <row r="43" spans="1:10" customHeight="1" ht="15">
-      <c r="A43" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-    </row>
-    <row r="44" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A44" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="29"/>
-      <c r="J44" s="2"/>
-    </row>
-    <row r="45" spans="1:10" customHeight="1" ht="27">
-      <c r="A45" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-    </row>
-    <row r="46" spans="1:10" customHeight="1" ht="15">
-      <c r="A46" s="30"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-    </row>
-    <row r="47" spans="1:10" customHeight="1" ht="39">
-      <c r="A47" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-    </row>
-    <row r="48" spans="1:10" customHeight="1" ht="15">
-      <c r="A48" s="32"/>
-      <c r="B48" s="32"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="33"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
-    </row>
-    <row r="49" spans="1:10" customHeight="1" ht="15">
-      <c r="A49" s="2"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="33"/>
-      <c r="I49" s="33"/>
-    </row>
-    <row r="50" spans="1:10" customHeight="1" ht="15">
-      <c r="A50" s="32"/>
-      <c r="B50" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="C50" s="34"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="H50" s="35"/>
-      <c r="I50" s="35"/>
-    </row>
-    <row r="51" spans="1:10" customHeight="1" ht="15">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-    </row>
-    <row r="52" spans="1:10" customHeight="1" ht="15">
-      <c r="A52" s="2"/>
-      <c r="B52" s="37"/>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="37"/>
-      <c r="H52" s="37"/>
-      <c r="I52" s="37"/>
-    </row>
-    <row r="53" spans="1:10" customHeight="1" ht="15">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-    </row>
-    <row r="54" spans="1:10" customHeight="1" ht="15">
-      <c r="A54" s="2"/>
-      <c r="B54" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="C54" s="34"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="34" t="str">
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="34" t="str">
         <f>C10</f>
         <v>Abraham Palayot Sanchez</v>
       </c>
-      <c r="H54" s="34"/>
-      <c r="I54" s="34"/>
-    </row>
-    <row r="55" spans="1:10" customHeight="1" ht="15">
-      <c r="A55" s="2"/>
-      <c r="B55" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C55" s="34"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="34" t="str">
+      <c r="H38" s="34"/>
+      <c r="I38" s="34"/>
+    </row>
+    <row r="39" spans="1:10" customHeight="1" ht="15">
+      <c r="A39" s="2"/>
+      <c r="B39" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="34" t="str">
         <f>C12</f>
         <v>Coordinador de Información Financiera</v>
       </c>
-      <c r="H55" s="34"/>
-      <c r="I55" s="34"/>
-    </row>
-    <row r="56" spans="1:10" customHeight="1" ht="15">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="32"/>
-    </row>
-    <row r="57" spans="1:10" customHeight="1" ht="15">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-    </row>
-    <row r="58" spans="1:10" customHeight="1" ht="15">
-      <c r="A58" s="32"/>
-      <c r="B58" s="32"/>
-      <c r="C58" s="32"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="34"/>
+    </row>
+    <row r="40" spans="1:10" customHeight="1" ht="15">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+    </row>
+    <row r="41" spans="1:10" customHeight="1" ht="15">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" spans="1:10" customHeight="1" ht="15">
+      <c r="A42" s="32"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1755,78 +1269,30 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="A39:I39"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A47:I47"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="G50:I50"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="G39:I39"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="H20:I20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H19:I36"/>
+    <mergeCell ref="H19:I20"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="87">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>25/04/2025</t>
+    <t>28/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -86,16 +86,163 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>DELL</t>
+  </si>
+  <si>
+    <t>Latitude 5520</t>
+  </si>
+  <si>
+    <t>FNY9FG3</t>
+  </si>
+  <si>
+    <t>64W9FG3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00008</t>
+  </si>
+  <si>
+    <t>Cargador Laptop</t>
+  </si>
+  <si>
+    <t>LA65NM190</t>
+  </si>
+  <si>
+    <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
+  </si>
+  <si>
+    <t>Teclado</t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>K120</t>
+  </si>
+  <si>
+    <t>1446MG00C698</t>
+  </si>
+  <si>
+    <t>MK235</t>
+  </si>
+  <si>
+    <t>2134MR38A788</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>M170</t>
+  </si>
+  <si>
+    <t>2131LZD121R8</t>
+  </si>
+  <si>
+    <t>Docking Station</t>
+  </si>
+  <si>
+    <t>WD19S</t>
+  </si>
+  <si>
+    <t>F9WQSB3</t>
+  </si>
+  <si>
+    <t>Cargador de Doking</t>
+  </si>
+  <si>
+    <t>HA180MP180</t>
+  </si>
+  <si>
+    <t>CN-03XYY8-CH200-17G-0BXA-A04</t>
+  </si>
+  <si>
     <t>Monitor</t>
   </si>
   <si>
-    <t>Dell</t>
-  </si>
-  <si>
     <t>E2724HS</t>
   </si>
   <si>
     <t>CN04XFCWTV2003AH0WDT</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>EliteDysplay E231</t>
+  </si>
+  <si>
+    <t>6CM4083FX3</t>
+  </si>
+  <si>
+    <t>Telefono</t>
+  </si>
+  <si>
+    <t>Polycom</t>
+  </si>
+  <si>
+    <t>VVX 150</t>
+  </si>
+  <si>
+    <t>64167F786244</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>5216 R</t>
+  </si>
+  <si>
+    <t>Unidad DVD</t>
+  </si>
+  <si>
+    <t>GP60NB50</t>
+  </si>
+  <si>
+    <t>CNH4306278</t>
+  </si>
+  <si>
+    <t>Audifonos</t>
+  </si>
+  <si>
+    <t>Poly</t>
+  </si>
+  <si>
+    <t>Voyager 5200</t>
+  </si>
+  <si>
+    <t>2X492H</t>
+  </si>
+  <si>
+    <t>Diadema</t>
+  </si>
+  <si>
+    <t>POLY</t>
+  </si>
+  <si>
+    <t>108DB1</t>
+  </si>
+  <si>
+    <t>2032CW</t>
+  </si>
+  <si>
+    <t>Cargador de Laptop</t>
+  </si>
+  <si>
+    <t>HSTNN-DA40</t>
+  </si>
+  <si>
+    <t>WDWRT0AAR6Z19W</t>
+  </si>
+  <si>
+    <t>DA65NM190</t>
+  </si>
+  <si>
+    <t>CN-0FTTTJ-DES00-14U-C63H-A01</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -967,290 +1114,624 @@
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22">
-        <v>123</v>
-      </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
+      <c r="A20" s="38">
+        <v>2</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="15">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
+      <c r="A22" s="38">
+        <v>3</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="15">
-      <c r="A23" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
+      <c r="A23" s="38">
+        <v>4</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="15">
-      <c r="A24" s="27"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
+      <c r="A24" s="38">
+        <v>5</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
-      <c r="A25" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
+      <c r="A25" s="38">
+        <v>6</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="38">
+        <v>7</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+    </row>
+    <row r="27" spans="1:10" customHeight="1" ht="15">
+      <c r="A27" s="38">
+        <v>8</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+    </row>
+    <row r="28" spans="1:10" customHeight="1" ht="15">
+      <c r="A28" s="38">
+        <v>9</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+    </row>
+    <row r="29" spans="1:10" customHeight="1" ht="15">
+      <c r="A29" s="38">
+        <v>10</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
+    </row>
+    <row r="30" spans="1:10" customHeight="1" ht="15">
+      <c r="A30" s="38">
+        <v>11</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+    </row>
+    <row r="31" spans="1:10" customHeight="1" ht="15">
+      <c r="A31" s="38">
+        <v>12</v>
+      </c>
+      <c r="B31" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+    </row>
+    <row r="32" spans="1:10" customHeight="1" ht="15">
+      <c r="A32" s="38">
+        <v>13</v>
+      </c>
+      <c r="B32" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+    </row>
+    <row r="33" spans="1:10" customHeight="1" ht="15">
+      <c r="A33" s="38">
+        <v>14</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="15">
+      <c r="A34" s="38">
+        <v>15</v>
+      </c>
+      <c r="B34" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="38"/>
+    </row>
+    <row r="35" spans="1:10" customHeight="1" ht="15">
+      <c r="A35" s="38">
+        <v>16</v>
+      </c>
+      <c r="B35" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
+    </row>
+    <row r="36" spans="1:10" customHeight="1" ht="15">
+      <c r="A36" s="38">
+        <v>17</v>
+      </c>
+      <c r="B36" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-    </row>
-    <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-    </row>
-    <row r="28" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A28" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="2"/>
-    </row>
-    <row r="29" spans="1:10" customHeight="1" ht="27">
-      <c r="A29" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-    </row>
-    <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="30"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-    </row>
-    <row r="31" spans="1:10" customHeight="1" ht="39">
-      <c r="A31" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-    </row>
-    <row r="32" spans="1:10" customHeight="1" ht="15">
-      <c r="A32" s="32"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-    </row>
-    <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="2"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="32"/>
-      <c r="B34" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="H34" s="35"/>
-      <c r="I34" s="35"/>
-    </row>
-    <row r="35" spans="1:10" customHeight="1" ht="15">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-    </row>
-    <row r="36" spans="1:10" customHeight="1" ht="15">
-      <c r="A36" s="2"/>
-      <c r="B36" s="37"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="37"/>
-      <c r="H36" s="37"/>
-      <c r="I36" s="37"/>
+      <c r="C36" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
+      <c r="A37" s="16"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="2"/>
-      <c r="B38" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="34" t="str">
+      <c r="A38" s="25"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="25"/>
+    </row>
+    <row r="39" spans="1:10" customHeight="1" ht="15">
+      <c r="A39" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+    </row>
+    <row r="40" spans="1:10" customHeight="1" ht="15">
+      <c r="A40" s="27"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+    </row>
+    <row r="41" spans="1:10" customHeight="1" ht="15">
+      <c r="A41" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="28"/>
+    </row>
+    <row r="42" spans="1:10" customHeight="1" ht="15">
+      <c r="A42" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+    </row>
+    <row r="43" spans="1:10" customHeight="1" ht="15">
+      <c r="A43" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+    </row>
+    <row r="44" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A44" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="2"/>
+    </row>
+    <row r="45" spans="1:10" customHeight="1" ht="27">
+      <c r="A45" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
+    </row>
+    <row r="46" spans="1:10" customHeight="1" ht="15">
+      <c r="A46" s="30"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+    </row>
+    <row r="47" spans="1:10" customHeight="1" ht="39">
+      <c r="A47" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31"/>
+      <c r="I47" s="31"/>
+    </row>
+    <row r="48" spans="1:10" customHeight="1" ht="15">
+      <c r="A48" s="32"/>
+      <c r="B48" s="32"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="33"/>
+      <c r="H48" s="33"/>
+      <c r="I48" s="33"/>
+    </row>
+    <row r="49" spans="1:10" customHeight="1" ht="15">
+      <c r="A49" s="2"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="33"/>
+      <c r="I49" s="33"/>
+    </row>
+    <row r="50" spans="1:10" customHeight="1" ht="15">
+      <c r="A50" s="32"/>
+      <c r="B50" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C50" s="34"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="H50" s="35"/>
+      <c r="I50" s="35"/>
+    </row>
+    <row r="51" spans="1:10" customHeight="1" ht="15">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="1:10" customHeight="1" ht="15">
+      <c r="A52" s="2"/>
+      <c r="B52" s="37"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="37"/>
+      <c r="H52" s="37"/>
+      <c r="I52" s="37"/>
+    </row>
+    <row r="53" spans="1:10" customHeight="1" ht="15">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+    </row>
+    <row r="54" spans="1:10" customHeight="1" ht="15">
+      <c r="A54" s="2"/>
+      <c r="B54" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="34" t="str">
         <f>C10</f>
         <v>Abraham Palayot Sanchez</v>
       </c>
-      <c r="H38" s="34"/>
-      <c r="I38" s="34"/>
-    </row>
-    <row r="39" spans="1:10" customHeight="1" ht="15">
-      <c r="A39" s="2"/>
-      <c r="B39" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="34" t="str">
+      <c r="H54" s="34"/>
+      <c r="I54" s="34"/>
+    </row>
+    <row r="55" spans="1:10" customHeight="1" ht="15">
+      <c r="A55" s="2"/>
+      <c r="B55" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="34" t="str">
         <f>C12</f>
         <v>Coordinador de Información Financiera</v>
       </c>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
-    </row>
-    <row r="40" spans="1:10" customHeight="1" ht="15">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
-    </row>
-    <row r="41" spans="1:10" customHeight="1" ht="15">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-    </row>
-    <row r="42" spans="1:10" customHeight="1" ht="15">
-      <c r="A42" s="32"/>
-      <c r="B42" s="32"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="34"/>
+    </row>
+    <row r="56" spans="1:10" customHeight="1" ht="15">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+    </row>
+    <row r="57" spans="1:10" customHeight="1" ht="15">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+    </row>
+    <row r="58" spans="1:10" customHeight="1" ht="15">
+      <c r="A58" s="32"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1269,30 +1750,78 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A30:I30"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="A46:I46"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="G55:I55"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H19:I20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H19:I36"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="88">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>28/04/2025</t>
+    <t>30/04/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>1446MG00C698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teclado </t>
   </si>
   <si>
     <t>MK235</t>
@@ -1194,17 +1197,17 @@
         <v>5</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C24" s="38" t="s">
         <v>32</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1215,17 +1218,17 @@
         <v>6</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C25" s="38" t="s">
         <v>32</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1236,17 +1239,17 @@
         <v>7</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C26" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
@@ -1257,17 +1260,17 @@
         <v>8</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C27" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
@@ -1278,17 +1281,17 @@
         <v>9</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C28" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E28" s="38"/>
       <c r="F28" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1299,17 +1302,17 @@
         <v>10</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
@@ -1320,17 +1323,17 @@
         <v>11</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="38"/>
@@ -1341,13 +1344,13 @@
         <v>12</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E31" s="38"/>
       <c r="F31" s="38"/>
@@ -1360,17 +1363,17 @@
         <v>13</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E32" s="38"/>
       <c r="F32" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G32" s="38"/>
       <c r="H32" s="38"/>
@@ -1381,17 +1384,17 @@
         <v>14</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D33" s="38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E33" s="38"/>
       <c r="F33" s="38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G33" s="38"/>
       <c r="H33" s="38"/>
@@ -1402,17 +1405,17 @@
         <v>15</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E34" s="38"/>
       <c r="F34" s="38" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G34" s="38"/>
       <c r="H34" s="38"/>
@@ -1423,17 +1426,17 @@
         <v>16</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E35" s="38"/>
       <c r="F35" s="38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G35" s="38"/>
       <c r="H35" s="38"/>
@@ -1450,11 +1453,11 @@
         <v>23</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E36" s="38"/>
       <c r="F36" s="38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G36" s="38"/>
       <c r="H36" s="38"/>
@@ -1484,7 +1487,7 @@
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B39" s="26"/>
       <c r="C39" s="26"/>
@@ -1508,7 +1511,7 @@
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="28" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B41" s="28"/>
       <c r="C41" s="28"/>
@@ -1521,7 +1524,7 @@
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B42" s="28"/>
       <c r="C42" s="28"/>
@@ -1534,7 +1537,7 @@
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B43" s="28"/>
       <c r="C43" s="28"/>
@@ -1547,7 +1550,7 @@
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="24.05">
       <c r="A44" s="29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B44" s="29"/>
       <c r="C44" s="29"/>
@@ -1561,7 +1564,7 @@
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="27">
       <c r="A45" s="28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B45" s="28"/>
       <c r="C45" s="28"/>
@@ -1585,7 +1588,7 @@
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="39">
       <c r="A47" s="31" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B47" s="31"/>
       <c r="C47" s="31"/>
@@ -1621,14 +1624,14 @@
     <row r="50" spans="1:10" customHeight="1" ht="15">
       <c r="A50" s="32"/>
       <c r="B50" s="34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C50" s="34"/>
       <c r="D50" s="34"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H50" s="35"/>
       <c r="I50" s="35"/>
@@ -1638,7 +1641,7 @@
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="36" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -1671,7 +1674,7 @@
     <row r="54" spans="1:10" customHeight="1" ht="15">
       <c r="A54" s="2"/>
       <c r="B54" s="34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C54" s="34"/>
       <c r="D54" s="34"/>
@@ -1687,7 +1690,7 @@
     <row r="55" spans="1:10" customHeight="1" ht="15">
       <c r="A55" s="2"/>
       <c r="B55" s="34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C55" s="34"/>
       <c r="D55" s="34"/>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -278,10 +278,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Alejandro Cancino Arguello</t>
-  </si>
-  <si>
-    <t>Supervisor TI</t>
+    <t>Alan Bauza Valdez</t>
+  </si>
+  <si>
+    <t>Supervisor Operaciones</t>
   </si>
 </sst>
 </file>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="74">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>30/04/2025</t>
+    <t>19/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -95,24 +95,12 @@
     <t>Latitude 5520</t>
   </si>
   <si>
-    <t>FNY9FG3</t>
-  </si>
-  <si>
     <t>64W9FG3</t>
   </si>
   <si>
     <t>DVZ-VH-TI-00008</t>
   </si>
   <si>
-    <t>Cargador Laptop</t>
-  </si>
-  <si>
-    <t>LA65NM190</t>
-  </si>
-  <si>
-    <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
-  </si>
-  <si>
     <t>Teclado</t>
   </si>
   <si>
@@ -125,9 +113,6 @@
     <t>1446MG00C698</t>
   </si>
   <si>
-    <t xml:space="preserve">Teclado </t>
-  </si>
-  <si>
     <t>MK235</t>
   </si>
   <si>
@@ -152,7 +137,7 @@
     <t>F9WQSB3</t>
   </si>
   <si>
-    <t>Cargador de Doking</t>
+    <t>Cargador de Docking</t>
   </si>
   <si>
     <t>HA180MP180</t>
@@ -170,39 +155,24 @@
     <t>CN04XFCWTV2003AH0WDT</t>
   </si>
   <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>5216 R</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Unidad DVD</t>
+  </si>
+  <si>
     <t>HP</t>
   </si>
   <si>
-    <t>EliteDysplay E231</t>
-  </si>
-  <si>
-    <t>6CM4083FX3</t>
-  </si>
-  <si>
-    <t>Telefono</t>
-  </si>
-  <si>
-    <t>Polycom</t>
-  </si>
-  <si>
-    <t>VVX 150</t>
-  </si>
-  <si>
-    <t>64167F786244</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>KOBLENZ</t>
-  </si>
-  <si>
-    <t>5216 R</t>
-  </si>
-  <si>
-    <t>Unidad DVD</t>
-  </si>
-  <si>
     <t>GP60NB50</t>
   </si>
   <si>
@@ -221,18 +191,6 @@
     <t>2X492H</t>
   </si>
   <si>
-    <t>Diadema</t>
-  </si>
-  <si>
-    <t>POLY</t>
-  </si>
-  <si>
-    <t>108DB1</t>
-  </si>
-  <si>
-    <t>2032CW</t>
-  </si>
-  <si>
     <t>Cargador de Laptop</t>
   </si>
   <si>
@@ -278,10 +236,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Alan Bauza Valdez</t>
-  </si>
-  <si>
-    <t>Supervisor Operaciones</t>
+    <t>Alejandro Cancino Arguello</t>
+  </si>
+  <si>
+    <t>Coordinador de TI</t>
   </si>
 </sst>
 </file>
@@ -1117,55 +1075,55 @@
       <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
-      <c r="A20" s="38">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+    </row>
+    <row r="21" spans="1:10" customHeight="1" ht="15">
+      <c r="A21" s="38">
         <v>2</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-    </row>
-    <row r="21" spans="1:10" customHeight="1" ht="15">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22" t="s">
+      <c r="B21" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
+      <c r="C21" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
       <c r="A22" s="38">
         <v>3</v>
       </c>
       <c r="B22" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="38" t="s">
-        <v>23</v>
-      </c>
       <c r="D22" s="38" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="38" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G22" s="38"/>
       <c r="H22" s="38"/>
@@ -1176,17 +1134,17 @@
         <v>4</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1197,17 +1155,17 @@
         <v>5</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1218,17 +1176,17 @@
         <v>6</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1239,17 +1197,17 @@
         <v>7</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C26" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
@@ -1260,17 +1218,17 @@
         <v>8</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
@@ -1281,17 +1239,17 @@
         <v>9</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E28" s="38"/>
       <c r="F28" s="38" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
@@ -1302,17 +1260,17 @@
         <v>10</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="38" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
@@ -1323,17 +1281,17 @@
         <v>11</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="38" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="38"/>
@@ -1347,394 +1305,291 @@
         <v>57</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
+      <c r="F31" s="38" t="s">
+        <v>61</v>
+      </c>
       <c r="G31" s="38"/>
       <c r="H31" s="38"/>
       <c r="I31" s="38"/>
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
-      <c r="A32" s="38">
-        <v>13</v>
-      </c>
-      <c r="B32" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38" t="s">
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+    </row>
+    <row r="33" spans="1:10" customHeight="1" ht="15">
+      <c r="A33" s="25"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="15">
+      <c r="A34" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="38"/>
-    </row>
-    <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="38">
-        <v>14</v>
-      </c>
-      <c r="B33" s="38" t="s">
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+    </row>
+    <row r="35" spans="1:10" customHeight="1" ht="15">
+      <c r="A35" s="27"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="27"/>
+    </row>
+    <row r="36" spans="1:10" customHeight="1" ht="15">
+      <c r="A36" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="38" t="s">
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+    </row>
+    <row r="37" spans="1:10" customHeight="1" ht="15">
+      <c r="A37" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="D33" s="38" t="s">
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+    </row>
+    <row r="38" spans="1:10" customHeight="1" ht="15">
+      <c r="A38" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38" t="s">
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+    </row>
+    <row r="39" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A39" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="G33" s="38"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="38">
-        <v>15</v>
-      </c>
-      <c r="B34" s="38" t="s">
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" spans="1:10" customHeight="1" ht="27">
+      <c r="A40" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="38" t="s">
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+    </row>
+    <row r="41" spans="1:10" customHeight="1" ht="15">
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="30"/>
+    </row>
+    <row r="42" spans="1:10" customHeight="1" ht="39">
+      <c r="A42" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="38" t="s">
+      <c r="B42" s="31"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+    </row>
+    <row r="43" spans="1:10" customHeight="1" ht="15">
+      <c r="A43" s="32"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
+    </row>
+    <row r="44" spans="1:10" customHeight="1" ht="15">
+      <c r="A44" s="2"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="33"/>
+      <c r="I44" s="33"/>
+    </row>
+    <row r="45" spans="1:10" customHeight="1" ht="15">
+      <c r="A45" s="32"/>
+      <c r="B45" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38" t="s">
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="38"/>
-    </row>
-    <row r="35" spans="1:10" customHeight="1" ht="15">
-      <c r="A35" s="38">
-        <v>16</v>
-      </c>
-      <c r="B35" s="38" t="s">
+      <c r="H45" s="35"/>
+      <c r="I45" s="35"/>
+    </row>
+    <row r="46" spans="1:10" customHeight="1" ht="15">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="D35" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="38"/>
-    </row>
-    <row r="36" spans="1:10" customHeight="1" ht="15">
-      <c r="A36" s="38">
-        <v>17</v>
-      </c>
-      <c r="B36" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D36" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-    </row>
-    <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="16"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-    </row>
-    <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="25"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
-    </row>
-    <row r="39" spans="1:10" customHeight="1" ht="15">
-      <c r="A39" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-    </row>
-    <row r="40" spans="1:10" customHeight="1" ht="15">
-      <c r="A40" s="27"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-    </row>
-    <row r="41" spans="1:10" customHeight="1" ht="15">
-      <c r="A41" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-    </row>
-    <row r="42" spans="1:10" customHeight="1" ht="15">
-      <c r="A42" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-    </row>
-    <row r="43" spans="1:10" customHeight="1" ht="15">
-      <c r="A43" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-    </row>
-    <row r="44" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A44" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="29"/>
-      <c r="J44" s="2"/>
-    </row>
-    <row r="45" spans="1:10" customHeight="1" ht="27">
-      <c r="A45" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-    </row>
-    <row r="46" spans="1:10" customHeight="1" ht="15">
-      <c r="A46" s="30"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-    </row>
-    <row r="47" spans="1:10" customHeight="1" ht="39">
-      <c r="A47" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+    </row>
+    <row r="47" spans="1:10" customHeight="1" ht="15">
+      <c r="A47" s="2"/>
+      <c r="B47" s="37"/>
+      <c r="C47" s="37"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="37"/>
+      <c r="I47" s="37"/>
     </row>
     <row r="48" spans="1:10" customHeight="1" ht="15">
-      <c r="A48" s="32"/>
-      <c r="B48" s="32"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="33"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15">
       <c r="A49" s="2"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
+      <c r="B49" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="33"/>
-      <c r="I49" s="33"/>
+      <c r="G49" s="34" t="str">
+        <f>C10</f>
+        <v>Abraham Palayot Sanchez</v>
+      </c>
+      <c r="H49" s="34"/>
+      <c r="I49" s="34"/>
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15">
-      <c r="A50" s="32"/>
+      <c r="A50" s="2"/>
       <c r="B50" s="34" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C50" s="34"/>
       <c r="D50" s="34"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
-      <c r="G50" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="H50" s="35"/>
-      <c r="I50" s="35"/>
+      <c r="G50" s="34" t="str">
+        <f>C12</f>
+        <v>Coordinador de Información Financiera</v>
+      </c>
+      <c r="H50" s="34"/>
+      <c r="I50" s="34"/>
     </row>
     <row r="51" spans="1:10" customHeight="1" ht="15">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="36" t="s">
-        <v>85</v>
-      </c>
+      <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
     </row>
     <row r="52" spans="1:10" customHeight="1" ht="15">
       <c r="A52" s="2"/>
-      <c r="B52" s="37"/>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
-      <c r="G52" s="37"/>
-      <c r="H52" s="37"/>
-      <c r="I52" s="37"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
     </row>
     <row r="53" spans="1:10" customHeight="1" ht="15">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
+      <c r="A53" s="32"/>
+      <c r="B53" s="32"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
-    </row>
-    <row r="54" spans="1:10" customHeight="1" ht="15">
-      <c r="A54" s="2"/>
-      <c r="B54" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="C54" s="34"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="34" t="str">
-        <f>C10</f>
-        <v>Abraham Palayot Sanchez</v>
-      </c>
-      <c r="H54" s="34"/>
-      <c r="I54" s="34"/>
-    </row>
-    <row r="55" spans="1:10" customHeight="1" ht="15">
-      <c r="A55" s="2"/>
-      <c r="B55" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C55" s="34"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="34" t="str">
-        <f>C12</f>
-        <v>Coordinador de Información Financiera</v>
-      </c>
-      <c r="H55" s="34"/>
-      <c r="I55" s="34"/>
-    </row>
-    <row r="56" spans="1:10" customHeight="1" ht="15">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="32"/>
-    </row>
-    <row r="57" spans="1:10" customHeight="1" ht="15">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-    </row>
-    <row r="58" spans="1:10" customHeight="1" ht="15">
-      <c r="A58" s="32"/>
-      <c r="B58" s="32"/>
-      <c r="C58" s="32"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1753,23 +1608,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A38:I38"/>
     <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A40:I40"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="G49:I49"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="G50:I50"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="G54:I54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="G55:I55"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1809,22 +1664,7 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="H31:I31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H19:I36"/>
+    <mergeCell ref="H19:I31"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>19/05/2025</t>
+    <t>21/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -50,7 +50,7 @@
     <t>Área:</t>
   </si>
   <si>
-    <t>Coordinador de Información Financiera</t>
+    <t>Supervisor de Información Financiera</t>
   </si>
   <si>
     <t>Región:</t>
@@ -167,33 +167,24 @@
     <t>NA</t>
   </si>
   <si>
-    <t>Unidad DVD</t>
+    <t>Audifonos</t>
+  </si>
+  <si>
+    <t>Poly</t>
+  </si>
+  <si>
+    <t>Voyager 5200</t>
+  </si>
+  <si>
+    <t>2X492H</t>
+  </si>
+  <si>
+    <t>Cargador de Laptop</t>
   </si>
   <si>
     <t>HP</t>
   </si>
   <si>
-    <t>GP60NB50</t>
-  </si>
-  <si>
-    <t>CNH4306278</t>
-  </si>
-  <si>
-    <t>Audifonos</t>
-  </si>
-  <si>
-    <t>Poly</t>
-  </si>
-  <si>
-    <t>Voyager 5200</t>
-  </si>
-  <si>
-    <t>2X492H</t>
-  </si>
-  <si>
-    <t>Cargador de Laptop</t>
-  </si>
-  <si>
     <t>HSTNN-DA40</t>
   </si>
   <si>
@@ -204,6 +195,15 @@
   </si>
   <si>
     <t>CN-0FTTTJ-DES00-14U-C63H-A01</t>
+  </si>
+  <si>
+    <t>Adaptador Multipuertos USB/HDMI/RJ45</t>
+  </si>
+  <si>
+    <t>ytfgijo</t>
+  </si>
+  <si>
+    <t>RCYTVUB</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -1281,17 +1281,17 @@
         <v>11</v>
       </c>
       <c r="B30" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="38" t="s">
         <v>57</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>58</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G30" s="38"/>
       <c r="H30" s="38"/>
@@ -1302,10 +1302,10 @@
         <v>12</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="D31" s="38" t="s">
         <v>60</v>
@@ -1553,7 +1553,7 @@
       <c r="F50" s="2"/>
       <c r="G50" s="34" t="str">
         <f>C12</f>
-        <v>Coordinador de Información Financiera</v>
+        <v>Supervisor de Información Financiera</v>
       </c>
       <c r="H50" s="34"/>
       <c r="I50" s="34"/>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>21/05/2025</t>
+    <t>10/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Sur</t>
+    <t>Norte</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -101,42 +101,6 @@
     <t>DVZ-VH-TI-00008</t>
   </si>
   <si>
-    <t>Teclado</t>
-  </si>
-  <si>
-    <t>Logitech</t>
-  </si>
-  <si>
-    <t>K120</t>
-  </si>
-  <si>
-    <t>1446MG00C698</t>
-  </si>
-  <si>
-    <t>MK235</t>
-  </si>
-  <si>
-    <t>2134MR38A788</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>M170</t>
-  </si>
-  <si>
-    <t>2131LZD121R8</t>
-  </si>
-  <si>
-    <t>Docking Station</t>
-  </si>
-  <si>
-    <t>WD19S</t>
-  </si>
-  <si>
-    <t>F9WQSB3</t>
-  </si>
-  <si>
     <t>Cargador de Docking</t>
   </si>
   <si>
@@ -236,10 +200,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Alejandro Cancino Arguello</t>
-  </si>
-  <si>
-    <t>Coordinador de TI</t>
+    <t>Cristobal Soto Escalante</t>
+  </si>
+  <si>
+    <t>Coordinador de Proyectos</t>
   </si>
 </sst>
 </file>
@@ -1095,14 +1059,14 @@
         <v>27</v>
       </c>
       <c r="C21" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="38" t="s">
         <v>28</v>
-      </c>
-      <c r="D21" s="38" t="s">
-        <v>29</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
@@ -1113,10 +1077,10 @@
         <v>3</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>31</v>
@@ -1137,14 +1101,14 @@
         <v>33</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1155,17 +1119,17 @@
         <v>5</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -1176,17 +1140,17 @@
         <v>6</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="38" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G25" s="38"/>
       <c r="H25" s="38"/>
@@ -1197,17 +1161,17 @@
         <v>7</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="38" t="s">
         <v>23</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="38" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
@@ -1218,155 +1182,124 @@
         <v>8</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G27" s="38"/>
       <c r="H27" s="38"/>
       <c r="I27" s="38"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="38">
-        <v>9</v>
-      </c>
-      <c r="B28" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="38" t="s">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
+    </row>
+    <row r="29" spans="1:10" customHeight="1" ht="15">
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+    </row>
+    <row r="30" spans="1:10" customHeight="1" ht="15">
+      <c r="A30" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+    </row>
+    <row r="31" spans="1:10" customHeight="1" ht="15">
+      <c r="A31" s="27"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+    </row>
+    <row r="32" spans="1:10" customHeight="1" ht="15">
+      <c r="A32" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38" t="s">
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+    </row>
+    <row r="33" spans="1:10" customHeight="1" ht="15">
+      <c r="A33" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-    </row>
-    <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="38">
-        <v>10</v>
-      </c>
-      <c r="B29" s="38" t="s">
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="15">
+      <c r="A34" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+    </row>
+    <row r="35" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A35" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="38" t="s">
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" spans="1:10" customHeight="1" ht="27">
+      <c r="A36" s="28" t="s">
         <v>55</v>
-      </c>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
-    </row>
-    <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="38">
-        <v>11</v>
-      </c>
-      <c r="B30" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-    </row>
-    <row r="31" spans="1:10" customHeight="1" ht="15">
-      <c r="A31" s="38">
-        <v>12</v>
-      </c>
-      <c r="B31" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
-    </row>
-    <row r="32" spans="1:10" customHeight="1" ht="15">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-    </row>
-    <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="25"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-    </row>
-    <row r="35" spans="1:10" customHeight="1" ht="15">
-      <c r="A35" s="27"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-    </row>
-    <row r="36" spans="1:10" customHeight="1" ht="15">
-      <c r="A36" s="28" t="s">
-        <v>63</v>
       </c>
       <c r="B36" s="28"/>
       <c r="C36" s="28"/>
@@ -1378,142 +1311,143 @@
       <c r="I36" s="28"/>
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-    </row>
-    <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-    </row>
-    <row r="39" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A39" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="29"/>
-      <c r="J39" s="2"/>
-    </row>
-    <row r="40" spans="1:10" customHeight="1" ht="27">
-      <c r="A40" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+    </row>
+    <row r="38" spans="1:10" customHeight="1" ht="39">
+      <c r="A38" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+    </row>
+    <row r="39" spans="1:10" customHeight="1" ht="15">
+      <c r="A39" s="32"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+    </row>
+    <row r="40" spans="1:10" customHeight="1" ht="15">
+      <c r="A40" s="2"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
-      <c r="A41" s="30"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="30"/>
-    </row>
-    <row r="42" spans="1:10" customHeight="1" ht="39">
-      <c r="A42" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
+      <c r="A41" s="32"/>
+      <c r="B41" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
+    </row>
+    <row r="42" spans="1:10" customHeight="1" ht="15">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
-      <c r="A43" s="32"/>
-      <c r="B43" s="32"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
+      <c r="A43" s="2"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
+      <c r="I43" s="37"/>
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="2"/>
-      <c r="B44" s="32"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
-      <c r="A45" s="32"/>
+      <c r="A45" s="2"/>
       <c r="B45" s="34" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C45" s="34"/>
       <c r="D45" s="34"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="H45" s="35"/>
-      <c r="I45" s="35"/>
+      <c r="G45" s="34" t="str">
+        <f>C10</f>
+        <v>Abraham Palayot Sanchez</v>
+      </c>
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
       <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="36" t="s">
-        <v>71</v>
-      </c>
+      <c r="B46" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
+      <c r="G46" s="34" t="str">
+        <f>C12</f>
+        <v>Supervisor de Información Financiera</v>
+      </c>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
       <c r="A47" s="2"/>
-      <c r="B47" s="37"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="37"/>
-      <c r="I47" s="37"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
     </row>
     <row r="48" spans="1:10" customHeight="1" ht="15">
       <c r="A48" s="2"/>
@@ -1527,69 +1461,15 @@
       <c r="I48" s="2"/>
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15">
-      <c r="A49" s="2"/>
-      <c r="B49" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
+      <c r="A49" s="32"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
-      <c r="G49" s="34" t="str">
-        <f>C10</f>
-        <v>Abraham Palayot Sanchez</v>
-      </c>
-      <c r="H49" s="34"/>
-      <c r="I49" s="34"/>
-    </row>
-    <row r="50" spans="1:10" customHeight="1" ht="15">
-      <c r="A50" s="2"/>
-      <c r="B50" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C50" s="34"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="34" t="str">
-        <f>C12</f>
-        <v>Supervisor de Información Financiera</v>
-      </c>
-      <c r="H50" s="34"/>
-      <c r="I50" s="34"/>
-    </row>
-    <row r="51" spans="1:10" customHeight="1" ht="15">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32"/>
-      <c r="I51" s="32"/>
-    </row>
-    <row r="52" spans="1:10" customHeight="1" ht="15">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-    </row>
-    <row r="53" spans="1:10" customHeight="1" ht="15">
-      <c r="A53" s="32"/>
-      <c r="B53" s="32"/>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1608,23 +1488,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="A37:I37"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A39:I39"/>
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="G41:I41"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="G45:I45"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="G46:I46"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1652,19 +1532,7 @@
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="H27:I27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H19:I31"/>
+    <mergeCell ref="H19:I27"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="52">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>10/06/2025</t>
+    <t>11/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -56,7 +56,7 @@
     <t>Región:</t>
   </si>
   <si>
-    <t>Norte</t>
+    <t>Sur</t>
   </si>
   <si>
     <t>Ubicación:</t>
@@ -101,48 +101,6 @@
     <t>DVZ-VH-TI-00008</t>
   </si>
   <si>
-    <t>Cargador de Docking</t>
-  </si>
-  <si>
-    <t>HA180MP180</t>
-  </si>
-  <si>
-    <t>CN-03XYY8-CH200-17G-0BXA-A04</t>
-  </si>
-  <si>
-    <t>Monitor</t>
-  </si>
-  <si>
-    <t>E2724HS</t>
-  </si>
-  <si>
-    <t>CN04XFCWTV2003AH0WDT</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>KOBLENZ</t>
-  </si>
-  <si>
-    <t>5216 R</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Audifonos</t>
-  </si>
-  <si>
-    <t>Poly</t>
-  </si>
-  <si>
-    <t>Voyager 5200</t>
-  </si>
-  <si>
-    <t>2X492H</t>
-  </si>
-  <si>
     <t>Cargador de Laptop</t>
   </si>
   <si>
@@ -170,6 +128,18 @@
     <t>RCYTVUB</t>
   </si>
   <si>
+    <t>Portátil</t>
+  </si>
+  <si>
+    <t>Kenwood</t>
+  </si>
+  <si>
+    <t>NX-340-K2</t>
+  </si>
+  <si>
+    <t>B9411672</t>
+  </si>
+  <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
   </si>
   <si>
@@ -200,10 +170,10 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Cristobal Soto Escalante</t>
-  </si>
-  <si>
-    <t>Coordinador de Proyectos</t>
+    <t>Alejandro Cancino Arguello</t>
+  </si>
+  <si>
+    <t>Coordinador de TI</t>
   </si>
 </sst>
 </file>
@@ -1059,14 +1029,14 @@
         <v>27</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
@@ -1077,7 +1047,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C22" s="38" t="s">
         <v>23</v>
@@ -1101,14 +1071,14 @@
         <v>33</v>
       </c>
       <c r="C23" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="38" t="s">
         <v>34</v>
-      </c>
-      <c r="D23" s="38" t="s">
-        <v>35</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G23" s="38"/>
       <c r="H23" s="38"/>
@@ -1119,147 +1089,124 @@
         <v>5</v>
       </c>
       <c r="B24" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="D24" s="38" t="s">
         <v>38</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>39</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
       <c r="I24" s="38"/>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
-      <c r="A25" s="38">
-        <v>6</v>
-      </c>
-      <c r="B25" s="38" t="s">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+    </row>
+    <row r="26" spans="1:10" customHeight="1" ht="15">
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+    </row>
+    <row r="27" spans="1:10" customHeight="1" ht="15">
+      <c r="A27" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+    </row>
+    <row r="28" spans="1:10" customHeight="1" ht="15">
+      <c r="A28" s="27"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+    </row>
+    <row r="29" spans="1:10" customHeight="1" ht="15">
+      <c r="A29" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+    </row>
+    <row r="30" spans="1:10" customHeight="1" ht="15">
+      <c r="A30" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="38" t="s">
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+    </row>
+    <row r="31" spans="1:10" customHeight="1" ht="15">
+      <c r="A31" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38" t="s">
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
+    </row>
+    <row r="32" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A32" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-    </row>
-    <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="38">
-        <v>7</v>
-      </c>
-      <c r="B26" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="38" t="s">
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" spans="1:10" customHeight="1" ht="27">
+      <c r="A33" s="28" t="s">
         <v>45</v>
-      </c>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-    </row>
-    <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="38">
-        <v>8</v>
-      </c>
-      <c r="B27" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="38"/>
-    </row>
-    <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-    </row>
-    <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="25"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
-    </row>
-    <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-    </row>
-    <row r="31" spans="1:10" customHeight="1" ht="15">
-      <c r="A31" s="27"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-    </row>
-    <row r="32" spans="1:10" customHeight="1" ht="15">
-      <c r="A32" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-    </row>
-    <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="28" t="s">
-        <v>52</v>
       </c>
       <c r="B33" s="28"/>
       <c r="C33" s="28"/>
@@ -1271,129 +1218,132 @@
       <c r="I33" s="28"/>
     </row>
     <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-    </row>
-    <row r="35" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A35" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="2"/>
-    </row>
-    <row r="36" spans="1:10" customHeight="1" ht="27">
-      <c r="A36" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+    </row>
+    <row r="35" spans="1:10" customHeight="1" ht="39">
+      <c r="A35" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
+    </row>
+    <row r="36" spans="1:10" customHeight="1" ht="15">
+      <c r="A36" s="32"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
     </row>
     <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="30"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-    </row>
-    <row r="38" spans="1:10" customHeight="1" ht="39">
-      <c r="A38" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31"/>
+      <c r="A37" s="2"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
+    </row>
+    <row r="38" spans="1:10" customHeight="1" ht="15">
+      <c r="A38" s="32"/>
+      <c r="B38" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
-      <c r="A39" s="32"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="36" t="s">
+        <v>49</v>
+      </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="33"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
       <c r="A40" s="2"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
+      <c r="G40" s="37"/>
+      <c r="H40" s="37"/>
+      <c r="I40" s="37"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
-      <c r="A41" s="32"/>
-      <c r="B41" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="H41" s="35"/>
-      <c r="I41" s="35"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="36" t="s">
-        <v>59</v>
-      </c>
+      <c r="B42" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
+      <c r="G42" s="34" t="str">
+        <f>C10</f>
+        <v>Abraham Palayot Sanchez</v>
+      </c>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
       <c r="A43" s="2"/>
-      <c r="B43" s="37"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
+      <c r="B43" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="37"/>
+      <c r="G43" s="34" t="str">
+        <f>C12</f>
+        <v>Supervisor de Información Financiera</v>
+      </c>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="2"/>
@@ -1402,74 +1352,31 @@
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="2"/>
-      <c r="B45" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="34" t="str">
-        <f>C10</f>
-        <v>Abraham Palayot Sanchez</v>
-      </c>
-      <c r="H45" s="34"/>
-      <c r="I45" s="34"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
-      <c r="A46" s="2"/>
-      <c r="B46" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
+      <c r="A46" s="32"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="34" t="str">
-        <f>C12</f>
-        <v>Supervisor de Información Financiera</v>
-      </c>
-      <c r="H46" s="34"/>
-      <c r="I46" s="34"/>
-    </row>
-    <row r="47" spans="1:10" customHeight="1" ht="15">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-    </row>
-    <row r="48" spans="1:10" customHeight="1" ht="15">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-    </row>
-    <row r="49" spans="1:10" customHeight="1" ht="15">
-      <c r="A49" s="32"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1488,23 +1395,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A29:I29"/>
     <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A31:I31"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="A38:I38"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="G41:I41"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="G45:I45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="G46:I46"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="G42:I42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="G43:I43"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1523,16 +1430,7 @@
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="H24:I24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H19:I27"/>
+    <mergeCell ref="H19:I24"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>11/06/2025</t>
+    <t>16/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -138,6 +138,27 @@
   </si>
   <si>
     <t>B9411672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adaptador de Puerto  </t>
+  </si>
+  <si>
+    <t>fctgyhu</t>
+  </si>
+  <si>
+    <t>FTUYGIBUNOI</t>
+  </si>
+  <si>
+    <t>Adaptador de puertos para MAC</t>
+  </si>
+  <si>
+    <t>Polycom</t>
+  </si>
+  <si>
+    <t>ygbuni</t>
+  </si>
+  <si>
+    <t>VUBHYIJNOK</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -1106,80 +1127,96 @@
       <c r="I24" s="38"/>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
+      <c r="A25" s="38">
+        <v>6</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
+      <c r="A26" s="38">
+        <v>7</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
+      <c r="A29" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
+      <c r="A30" s="27"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="28" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
@@ -1190,23 +1227,22 @@
       <c r="H31" s="28"/>
       <c r="I31" s="28"/>
     </row>
-    <row r="32" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A32" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" customHeight="1" ht="27">
+    <row r="32" spans="1:10" customHeight="1" ht="15">
+      <c r="A32" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+    </row>
+    <row r="33" spans="1:10" customHeight="1" ht="15">
       <c r="A33" s="28" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B33" s="28"/>
       <c r="C33" s="28"/>
@@ -1217,96 +1253,101 @@
       <c r="H33" s="28"/>
       <c r="I33" s="28"/>
     </row>
-    <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="30"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-    </row>
-    <row r="35" spans="1:10" customHeight="1" ht="39">
-      <c r="A35" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
+    <row r="34" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A34" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="1:10" customHeight="1" ht="27">
+      <c r="A35" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
-      <c r="A36" s="32"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-    </row>
-    <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="2"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+    </row>
+    <row r="37" spans="1:10" customHeight="1" ht="39">
+      <c r="A37" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
       <c r="A38" s="32"/>
-      <c r="B38" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="36" t="s">
-        <v>49</v>
-      </c>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
-      <c r="A40" s="2"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
+      <c r="A40" s="32"/>
+      <c r="B40" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37"/>
+      <c r="G40" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
+      <c r="D41" s="36" t="s">
+        <v>56</v>
+      </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -1315,68 +1356,90 @@
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="2"/>
-      <c r="B42" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="34" t="str">
+      <c r="G42" s="37"/>
+      <c r="H42" s="37"/>
+      <c r="I42" s="37"/>
+    </row>
+    <row r="43" spans="1:10" customHeight="1" ht="15">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+    </row>
+    <row r="44" spans="1:10" customHeight="1" ht="15">
+      <c r="A44" s="2"/>
+      <c r="B44" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="34" t="str">
         <f>C10</f>
         <v>Abraham Palayot Sanchez</v>
       </c>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-    </row>
-    <row r="43" spans="1:10" customHeight="1" ht="15">
-      <c r="A43" s="2"/>
-      <c r="B43" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="34" t="str">
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+    </row>
+    <row r="45" spans="1:10" customHeight="1" ht="15">
+      <c r="A45" s="2"/>
+      <c r="B45" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="34" t="str">
         <f>C12</f>
         <v>Supervisor de Información Financiera</v>
       </c>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-    </row>
-    <row r="44" spans="1:10" customHeight="1" ht="15">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
-    </row>
-    <row r="45" spans="1:10" customHeight="1" ht="15">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
-      <c r="A46" s="32"/>
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+    </row>
+    <row r="47" spans="1:10" customHeight="1" ht="15">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+    </row>
+    <row r="48" spans="1:10" customHeight="1" ht="15">
+      <c r="A48" s="32"/>
+      <c r="B48" s="32"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1395,23 +1458,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H27:I27"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A30:I30"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="G45:I45"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1430,7 +1493,13 @@
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H19:I24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H19:I26"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>27/06/2025</t>
+    <t>30/06/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>Telemetría</t>
+    <t>TI</t>
   </si>
   <si>
     <t>Región:</t>
@@ -92,12 +92,12 @@
     <t>Latitude 5520</t>
   </si>
   <si>
+    <t>1446MG00C698</t>
+  </si>
+  <si>
     <t>64W9FG3</t>
   </si>
   <si>
-    <t>Cambio de Laptop</t>
-  </si>
-  <si>
     <t>DVZ-VH-TI-00008</t>
   </si>
   <si>
@@ -195,6 +195,12 @@
   </si>
   <si>
     <t>Supervisor de Información Financiera</t>
+  </si>
+  <si>
+    <t>Rodrigo Suárez</t>
+  </si>
+  <si>
+    <t>PEMEX</t>
   </si>
 </sst>
 </file>
@@ -861,7 +867,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -1099,22 +1105,28 @@
         <v>25</v>
       </c>
       <c r="H17" s="53"/>
-      <c r="I17" s="53" t="s">
-        <v>26</v>
-      </c>
+      <c r="I17" s="53"/>
       <c r="J17" s="51"/>
       <c r="K17" s="17"/>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="52"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="51" t="s">
-        <v>27</v>
+      <c r="B18" s="53">
+        <v>2</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="53" t="s">
+        <v>24</v>
       </c>
       <c r="F18" s="53"/>
-      <c r="G18" s="53"/>
+      <c r="G18" s="53" t="s">
+        <v>26</v>
+      </c>
       <c r="H18" s="53"/>
       <c r="I18" s="53"/>
       <c r="J18" s="53"/>
@@ -1122,22 +1134,14 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="52"/>
-      <c r="B19" s="53">
-        <v>2</v>
-      </c>
-      <c r="C19" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="53" t="s">
-        <v>30</v>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="51" t="s">
+        <v>27</v>
       </c>
       <c r="F19" s="53"/>
-      <c r="G19" s="53" t="s">
-        <v>31</v>
-      </c>
+      <c r="G19" s="53"/>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
       <c r="J19" s="53"/>
@@ -1152,14 +1156,14 @@
         <v>28</v>
       </c>
       <c r="D20" s="53" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E20" s="53" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F20" s="53"/>
       <c r="G20" s="53" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H20" s="53"/>
       <c r="I20" s="53"/>
@@ -1172,17 +1176,17 @@
         <v>4</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="53" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H21" s="53"/>
       <c r="I21" s="53"/>
@@ -1195,17 +1199,17 @@
         <v>5</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F22" s="53"/>
       <c r="G22" s="53" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H22" s="53"/>
       <c r="I22" s="53"/>
@@ -1218,17 +1222,17 @@
         <v>6</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D23" s="53" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E23" s="53" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F23" s="53"/>
       <c r="G23" s="53" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
@@ -1241,103 +1245,112 @@
         <v>7</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D24" s="53" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E24" s="53" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F24" s="53"/>
       <c r="G24" s="53" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H24" s="53"/>
       <c r="I24" s="53"/>
       <c r="J24" s="53"/>
       <c r="K24" s="17"/>
     </row>
-    <row r="25" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A25" s="18"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="31"/>
+    <row r="25" spans="1:11">
+      <c r="A25" s="52"/>
+      <c r="B25" s="53">
+        <v>8</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="17"/>
     </row>
     <row r="26" spans="1:11" customHeight="1" ht="15.75">
       <c r="A26" s="18"/>
       <c r="B26" s="24"/>
       <c r="C26" s="24"/>
       <c r="D26" s="24"/>
-      <c r="E26" s="30"/>
+      <c r="E26" s="35"/>
       <c r="F26" s="31"/>
-      <c r="G26" s="32"/>
+      <c r="G26" s="35"/>
       <c r="H26" s="31"/>
-      <c r="I26" s="32"/>
+      <c r="I26" s="35"/>
       <c r="J26" s="31"/>
     </row>
     <row r="27" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="31"/>
     </row>
     <row r="28" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A28" s="19"/>
-      <c r="B28" s="33" t="s">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+    </row>
+    <row r="29" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A29" s="19"/>
+      <c r="B29" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-    </row>
-    <row r="29" spans="1:11" customHeight="1" ht="9">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-    </row>
-    <row r="30" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+    </row>
+    <row r="30" spans="1:11" customHeight="1" ht="9">
       <c r="A30" s="20"/>
-      <c r="B30" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-    </row>
-    <row r="31" spans="1:11" customHeight="1" ht="15">
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+    </row>
+    <row r="31" spans="1:11" customHeight="1" ht="15.75">
       <c r="A31" s="20"/>
       <c r="B31" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C31" s="26"/>
       <c r="D31" s="26"/>
@@ -1351,7 +1364,7 @@
     <row r="32" spans="1:11" customHeight="1" ht="15">
       <c r="A32" s="20"/>
       <c r="B32" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C32" s="26"/>
       <c r="D32" s="26"/>
@@ -1365,7 +1378,7 @@
     <row r="33" spans="1:11" customHeight="1" ht="15">
       <c r="A33" s="20"/>
       <c r="B33" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33" s="26"/>
       <c r="D33" s="26"/>
@@ -1379,7 +1392,7 @@
     <row r="34" spans="1:11" customHeight="1" ht="15">
       <c r="A34" s="20"/>
       <c r="B34" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
@@ -1390,9 +1403,11 @@
       <c r="I34" s="26"/>
       <c r="J34" s="26"/>
     </row>
-    <row r="35" spans="1:11" customHeight="1" ht="12">
-      <c r="A35" s="21"/>
-      <c r="B35" s="28"/>
+    <row r="35" spans="1:11" customHeight="1" ht="15">
+      <c r="A35" s="20"/>
+      <c r="B35" s="27" t="s">
+        <v>53</v>
+      </c>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
@@ -1402,11 +1417,9 @@
       <c r="I35" s="26"/>
       <c r="J35" s="26"/>
     </row>
-    <row r="36" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A36" s="17"/>
-      <c r="B36" s="29" t="s">
-        <v>54</v>
-      </c>
+    <row r="36" spans="1:11" customHeight="1" ht="12">
+      <c r="A36" s="21"/>
+      <c r="B36" s="28"/>
       <c r="C36" s="26"/>
       <c r="D36" s="26"/>
       <c r="E36" s="26"/>
@@ -1416,84 +1429,118 @@
       <c r="I36" s="26"/>
       <c r="J36" s="26"/>
     </row>
-    <row r="37" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
+    <row r="37" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A37" s="17"/>
+      <c r="B37" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
     </row>
     <row r="38" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
       <c r="C38" s="22"/>
       <c r="D38" s="22"/>
       <c r="E38" s="22"/>
+      <c r="H38" s="15"/>
       <c r="I38" s="15"/>
       <c r="J38" s="15"/>
     </row>
     <row r="39" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="25" t="s">
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+    </row>
+    <row r="40" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="H39" s="34" t="s">
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="H40" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-    </row>
-    <row r="40" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="41" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
-      <c r="J41" s="23"/>
-    </row>
-    <row r="42" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="43" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C43" s="25" t="s">
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
+    </row>
+    <row r="41" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="42" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="23"/>
+    </row>
+    <row r="43" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="44" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C44" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="H43" s="25" t="str">
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="H44" s="25" t="str">
         <f>C8</f>
         <v>Abraham Palayot Sanchez</v>
       </c>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
-    </row>
-    <row r="44" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C44" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="H44" s="25" t="s">
-        <v>59</v>
-      </c>
       <c r="I44" s="26"/>
       <c r="J44" s="26"/>
     </row>
     <row r="45" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H45" s="22"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="22"/>
-    </row>
-    <row r="46" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="47" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A47" s="22"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
+      <c r="C45" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="H45" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+    </row>
+    <row r="46" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H46" s="22"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="22"/>
+    </row>
+    <row r="47" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="48" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="F49" s="22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="F54" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="F55" s="22" t="s">
+        <v>61</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -1508,26 +1555,26 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="G26:H26"/>
     <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="H40:J40"/>
     <mergeCell ref="C44:E44"/>
     <mergeCell ref="H44:J44"/>
-    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="H45:J45"/>
     <mergeCell ref="B31:J31"/>
     <mergeCell ref="B32:J32"/>
     <mergeCell ref="B33:J33"/>
     <mergeCell ref="B34:J34"/>
     <mergeCell ref="B35:J35"/>
     <mergeCell ref="B36:J36"/>
+    <mergeCell ref="B37:J37"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -1552,7 +1599,10 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I17:J24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I17:J25"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="43">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,15 +41,12 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>30/06/2025</t>
+    <t>01/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>TI</t>
-  </si>
-  <si>
     <t>Región:</t>
   </si>
   <si>
@@ -59,9 +56,6 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>Base Operativa</t>
-  </si>
-  <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
   </si>
   <si>
@@ -92,9 +86,6 @@
     <t>Latitude 5520</t>
   </si>
   <si>
-    <t>1446MG00C698</t>
-  </si>
-  <si>
     <t>64W9FG3</t>
   </si>
   <si>
@@ -119,48 +110,6 @@
     <t>CN-0FTTTJ-DES00-14U-C63H-A01</t>
   </si>
   <si>
-    <t>Adaptador Multipuertos USB/HDMI/RJ45</t>
-  </si>
-  <si>
-    <t>ytfgijo</t>
-  </si>
-  <si>
-    <t>RCYTVUB</t>
-  </si>
-  <si>
-    <t>Portátil</t>
-  </si>
-  <si>
-    <t>Kenwood</t>
-  </si>
-  <si>
-    <t>NX-340-K2</t>
-  </si>
-  <si>
-    <t>B9411672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adaptador de Puerto  </t>
-  </si>
-  <si>
-    <t>fctgyhu</t>
-  </si>
-  <si>
-    <t>FTUYGIBUNOI</t>
-  </si>
-  <si>
-    <t>Adaptador de puertos para MAC</t>
-  </si>
-  <si>
-    <t>Polycom</t>
-  </si>
-  <si>
-    <t>ygbuni</t>
-  </si>
-  <si>
-    <t>VUBHYIJNOK</t>
-  </si>
-  <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
   </si>
   <si>
@@ -195,12 +144,6 @@
   </si>
   <si>
     <t>Supervisor de Información Financiera</t>
-  </si>
-  <si>
-    <t>Rodrigo Suárez</t>
-  </si>
-  <si>
-    <t>PEMEX</t>
   </si>
 </sst>
 </file>
@@ -867,7 +810,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -993,20 +936,20 @@
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="11">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>14</v>
+      <c r="J10" s="6">
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
@@ -1015,7 +958,7 @@
     <row r="12" spans="1:11" customHeight="1" ht="15.75">
       <c r="A12" s="13"/>
       <c r="B12" s="38" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
@@ -1064,24 +1007,24 @@
     <row r="16" spans="1:11" customHeight="1" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="E16" s="39" t="s">
         <v>17</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>19</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H16" s="40"/>
       <c r="I16" s="39" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J16" s="40"/>
       <c r="K16" s="17"/>
@@ -1092,17 +1035,17 @@
         <v>1</v>
       </c>
       <c r="C17" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="53" t="s">
         <v>22</v>
-      </c>
-      <c r="D17" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>24</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="53" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
@@ -1111,22 +1054,14 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="52"/>
-      <c r="B18" s="53">
-        <v>2</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="53" t="s">
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="51" t="s">
         <v>24</v>
       </c>
       <c r="F18" s="53"/>
-      <c r="G18" s="53" t="s">
-        <v>26</v>
-      </c>
+      <c r="G18" s="53"/>
       <c r="H18" s="53"/>
       <c r="I18" s="53"/>
       <c r="J18" s="53"/>
@@ -1134,14 +1069,22 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="52"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="51" t="s">
+      <c r="B19" s="53">
+        <v>2</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="53" t="s">
         <v>27</v>
       </c>
       <c r="F19" s="53"/>
-      <c r="G19" s="53"/>
+      <c r="G19" s="53" t="s">
+        <v>28</v>
+      </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
       <c r="J19" s="53"/>
@@ -1153,178 +1096,131 @@
         <v>3</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D20" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="53" t="s">
         <v>29</v>
-      </c>
-      <c r="E20" s="53" t="s">
-        <v>30</v>
       </c>
       <c r="F20" s="53"/>
       <c r="G20" s="53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H20" s="53"/>
       <c r="I20" s="53"/>
       <c r="J20" s="53"/>
       <c r="K20" s="17"/>
     </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="52"/>
-      <c r="B21" s="53">
-        <v>4</v>
-      </c>
-      <c r="C21" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="53" t="s">
+    <row r="21" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A21" s="18"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="31"/>
+    </row>
+    <row r="22" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A22" s="18"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="31"/>
+    </row>
+    <row r="23" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+    </row>
+    <row r="24" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A24" s="19"/>
+      <c r="B24" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+    </row>
+    <row r="25" spans="1:11" customHeight="1" ht="9">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A26" s="20"/>
+      <c r="B26" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53" t="s">
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+    </row>
+    <row r="27" spans="1:11" customHeight="1" ht="15">
+      <c r="A27" s="20"/>
+      <c r="B27" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="17"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="52"/>
-      <c r="B22" s="53">
-        <v>5</v>
-      </c>
-      <c r="C22" s="53" t="s">
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+    </row>
+    <row r="28" spans="1:11" customHeight="1" ht="15">
+      <c r="A28" s="20"/>
+      <c r="B28" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="53" t="s">
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+    </row>
+    <row r="29" spans="1:11" customHeight="1" ht="15">
+      <c r="A29" s="20"/>
+      <c r="B29" s="27" t="s">
         <v>35</v>
-      </c>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="17"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="52"/>
-      <c r="B23" s="53">
-        <v>6</v>
-      </c>
-      <c r="C23" s="53" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="17"/>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="52"/>
-      <c r="B24" s="53">
-        <v>7</v>
-      </c>
-      <c r="C24" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="53" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="17"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="52"/>
-      <c r="B25" s="53">
-        <v>8</v>
-      </c>
-      <c r="C25" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="E25" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="F25" s="53"/>
-      <c r="G25" s="53" t="s">
-        <v>47</v>
-      </c>
-      <c r="H25" s="53"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="17"/>
-    </row>
-    <row r="26" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A26" s="18"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="31"/>
-    </row>
-    <row r="27" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A27" s="18"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="31"/>
-    </row>
-    <row r="28" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-    </row>
-    <row r="29" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A29" s="19"/>
-      <c r="B29" s="33" t="s">
-        <v>48</v>
       </c>
       <c r="C29" s="26"/>
       <c r="D29" s="26"/>
@@ -1335,23 +1231,23 @@
       <c r="I29" s="26"/>
       <c r="J29" s="26"/>
     </row>
-    <row r="30" spans="1:11" customHeight="1" ht="9">
+    <row r="30" spans="1:11" customHeight="1" ht="15">
       <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-    </row>
-    <row r="31" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A31" s="20"/>
-      <c r="B31" s="27" t="s">
-        <v>49</v>
-      </c>
+      <c r="B30" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+    </row>
+    <row r="31" spans="1:11" customHeight="1" ht="12">
+      <c r="A31" s="21"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="26"/>
       <c r="D31" s="26"/>
       <c r="E31" s="26"/>
@@ -1361,10 +1257,10 @@
       <c r="I31" s="26"/>
       <c r="J31" s="26"/>
     </row>
-    <row r="32" spans="1:11" customHeight="1" ht="15">
-      <c r="A32" s="20"/>
-      <c r="B32" s="27" t="s">
-        <v>50</v>
+    <row r="32" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A32" s="17"/>
+      <c r="B32" s="29" t="s">
+        <v>37</v>
       </c>
       <c r="C32" s="26"/>
       <c r="D32" s="26"/>
@@ -1375,172 +1271,84 @@
       <c r="I32" s="26"/>
       <c r="J32" s="26"/>
     </row>
-    <row r="33" spans="1:11" customHeight="1" ht="15">
-      <c r="A33" s="20"/>
-      <c r="B33" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-    </row>
-    <row r="34" spans="1:11" customHeight="1" ht="15">
-      <c r="A34" s="20"/>
-      <c r="B34" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-    </row>
-    <row r="35" spans="1:11" customHeight="1" ht="15">
-      <c r="A35" s="20"/>
-      <c r="B35" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="26"/>
+    <row r="33" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+    </row>
+    <row r="34" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+    </row>
+    <row r="35" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="25" t="s">
+        <v>38</v>
+      </c>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
+      <c r="H35" s="34" t="s">
+        <v>39</v>
+      </c>
       <c r="I35" s="26"/>
       <c r="J35" s="26"/>
     </row>
-    <row r="36" spans="1:11" customHeight="1" ht="12">
-      <c r="A36" s="21"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-    </row>
-    <row r="37" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A37" s="17"/>
-      <c r="B37" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-    </row>
-    <row r="38" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-    </row>
+    <row r="36" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="37" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="23"/>
+      <c r="J37" s="23"/>
+    </row>
+    <row r="38" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="39" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
+      <c r="C39" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="H39" s="25" t="str">
+        <f>C8</f>
+        <v>Abraham Palayot Sanchez</v>
+      </c>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
     </row>
     <row r="40" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
       <c r="C40" s="25" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D40" s="26"/>
       <c r="E40" s="26"/>
-      <c r="H40" s="34" t="s">
-        <v>56</v>
+      <c r="H40" s="25" t="s">
+        <v>42</v>
       </c>
       <c r="I40" s="26"/>
       <c r="J40" s="26"/>
     </row>
-    <row r="41" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="42" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="23"/>
-    </row>
-    <row r="43" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="44" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C44" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="H44" s="25" t="str">
-        <f>C8</f>
-        <v>Abraham Palayot Sanchez</v>
-      </c>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
-    </row>
-    <row r="45" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C45" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="H45" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
-    </row>
-    <row r="46" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="22"/>
-    </row>
-    <row r="47" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="48" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A48" s="22"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="F49" s="22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-    </row>
-    <row r="54" spans="1:11">
-      <c r="F54" s="22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
-      <c r="F55" s="22" t="s">
-        <v>61</v>
-      </c>
+    <row r="41" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+    </row>
+    <row r="42" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="43" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -1555,26 +1363,26 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="H39:J39"/>
     <mergeCell ref="C40:E40"/>
     <mergeCell ref="H40:J40"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="B27:J27"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="B29:J29"/>
+    <mergeCell ref="B30:J30"/>
     <mergeCell ref="B31:J31"/>
     <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B33:J33"/>
-    <mergeCell ref="B34:J34"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="B37:J37"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -1587,22 +1395,7 @@
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="I20:J20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I17:J25"/>
+    <mergeCell ref="I17:J20"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,12 +41,15 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>01/07/2025</t>
+    <t>14/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
+    <t>TI</t>
+  </si>
+  <si>
     <t>Región:</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
     <t>Ubicación:</t>
   </si>
   <si>
+    <t>BASE OPERATIVA</t>
+  </si>
+  <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
   </si>
   <si>
@@ -86,6 +92,12 @@
     <t>Latitude 5520</t>
   </si>
   <si>
+    <t>1446MG00C698</t>
+  </si>
+  <si>
+    <t>Y8GS78BY8</t>
+  </si>
+  <si>
     <t>64W9FG3</t>
   </si>
   <si>
@@ -98,12 +110,48 @@
     <t>HP</t>
   </si>
   <si>
+    <t>LA65NM190</t>
+  </si>
+  <si>
+    <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
+  </si>
+  <si>
     <t>HSTNN-DA40</t>
   </si>
   <si>
     <t>WDWRT0AAR6Z19W</t>
   </si>
   <si>
+    <t>Impresora</t>
+  </si>
+  <si>
+    <t>EPSON</t>
+  </si>
+  <si>
+    <t>EconTank L6270</t>
+  </si>
+  <si>
+    <t>X8G5011801</t>
+  </si>
+  <si>
+    <t>Desktop/Monitor</t>
+  </si>
+  <si>
+    <t>Optiplex 7490 AIO</t>
+  </si>
+  <si>
+    <t>6TYKTH3</t>
+  </si>
+  <si>
+    <t>DVZ-VH-TI-00098</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
     <t>DA65NM190</t>
   </si>
   <si>
@@ -144,6 +192,12 @@
   </si>
   <si>
     <t>Supervisor de Información Financiera</t>
+  </si>
+  <si>
+    <t>Ricardo</t>
+  </si>
+  <si>
+    <t>Supervisor</t>
   </si>
 </sst>
 </file>
@@ -810,7 +864,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -936,20 +990,20 @@
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>11</v>
-      </c>
       <c r="I10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J10" s="6">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
@@ -958,7 +1012,7 @@
     <row r="12" spans="1:11" customHeight="1" ht="15.75">
       <c r="A12" s="13"/>
       <c r="B12" s="38" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
@@ -1007,24 +1061,24 @@
     <row r="16" spans="1:11" customHeight="1" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H16" s="40"/>
       <c r="I16" s="39" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J16" s="40"/>
       <c r="K16" s="17"/>
@@ -1035,17 +1089,17 @@
         <v>1</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E17" s="53" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="53" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
@@ -1058,7 +1112,7 @@
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
       <c r="E18" s="51" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F18" s="53"/>
       <c r="G18" s="53"/>
@@ -1073,17 +1127,17 @@
         <v>2</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F19" s="53"/>
       <c r="G19" s="53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
@@ -1092,162 +1146,213 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="52"/>
-      <c r="B20" s="53">
-        <v>3</v>
-      </c>
-      <c r="C20" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="53" t="s">
-        <v>29</v>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="51" t="s">
+        <v>28</v>
       </c>
       <c r="F20" s="53"/>
-      <c r="G20" s="53" t="s">
-        <v>30</v>
-      </c>
+      <c r="G20" s="53"/>
       <c r="H20" s="53"/>
       <c r="I20" s="53"/>
       <c r="J20" s="53"/>
       <c r="K20" s="17"/>
     </row>
-    <row r="21" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A21" s="18"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="31"/>
-    </row>
-    <row r="22" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A22" s="18"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="31"/>
-    </row>
-    <row r="23" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-    </row>
-    <row r="24" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A24" s="19"/>
-      <c r="B24" s="33" t="s">
+    <row r="21" spans="1:11">
+      <c r="A21" s="52"/>
+      <c r="B21" s="53">
+        <v>3</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
-    </row>
-    <row r="25" spans="1:11" customHeight="1" ht="9">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-    </row>
-    <row r="26" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A26" s="20"/>
-      <c r="B26" s="27" t="s">
+      <c r="F21" s="53"/>
+      <c r="G21" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-    </row>
-    <row r="27" spans="1:11" customHeight="1" ht="15">
-      <c r="A27" s="20"/>
-      <c r="B27" s="27" t="s">
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="17"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="52"/>
+      <c r="B22" s="53">
+        <v>4</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-    </row>
-    <row r="28" spans="1:11" customHeight="1" ht="15">
-      <c r="A28" s="20"/>
-      <c r="B28" s="27" t="s">
+      <c r="F22" s="53"/>
+      <c r="G22" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-    </row>
-    <row r="29" spans="1:11" customHeight="1" ht="15">
-      <c r="A29" s="20"/>
-      <c r="B29" s="27" t="s">
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="52"/>
+      <c r="B23" s="53">
+        <v>5</v>
+      </c>
+      <c r="C23" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-    </row>
-    <row r="30" spans="1:11" customHeight="1" ht="15">
-      <c r="A30" s="20"/>
-      <c r="B30" s="27" t="s">
+      <c r="D23" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-    </row>
-    <row r="31" spans="1:11" customHeight="1" ht="12">
-      <c r="A31" s="21"/>
-      <c r="B31" s="28"/>
+      <c r="E23" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="17"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="52"/>
+      <c r="B24" s="53">
+        <v>6</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="17"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="52"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="17"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="52"/>
+      <c r="B26" s="53">
+        <v>7</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="52"/>
+      <c r="B27" s="53">
+        <v>8</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A28" s="18"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="31"/>
+    </row>
+    <row r="29" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A29" s="18"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="31"/>
+    </row>
+    <row r="30" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+    </row>
+    <row r="31" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A31" s="19"/>
+      <c r="B31" s="33" t="s">
+        <v>47</v>
+      </c>
       <c r="C31" s="26"/>
       <c r="D31" s="26"/>
       <c r="E31" s="26"/>
@@ -1257,98 +1362,212 @@
       <c r="I31" s="26"/>
       <c r="J31" s="26"/>
     </row>
-    <row r="32" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A32" s="17"/>
-      <c r="B32" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
+    <row r="32" spans="1:11" customHeight="1" ht="9">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
     </row>
     <row r="33" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-    </row>
-    <row r="34" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-    </row>
-    <row r="35" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="25" t="s">
-        <v>38</v>
-      </c>
+      <c r="A33" s="20"/>
+      <c r="B33" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+    </row>
+    <row r="34" spans="1:11" customHeight="1" ht="15">
+      <c r="A34" s="20"/>
+      <c r="B34" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
+    </row>
+    <row r="35" spans="1:11" customHeight="1" ht="15">
+      <c r="A35" s="20"/>
+      <c r="B35" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="26"/>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
-      <c r="H35" s="34" t="s">
-        <v>39</v>
-      </c>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
       <c r="I35" s="26"/>
       <c r="J35" s="26"/>
     </row>
-    <row r="36" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="37" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
-      <c r="J37" s="23"/>
-    </row>
-    <row r="38" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="39" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C39" s="25" t="s">
-        <v>40</v>
-      </c>
+    <row r="36" spans="1:11" customHeight="1" ht="15">
+      <c r="A36" s="20"/>
+      <c r="B36" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+    </row>
+    <row r="37" spans="1:11" customHeight="1" ht="15">
+      <c r="A37" s="20"/>
+      <c r="B37" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+    </row>
+    <row r="38" spans="1:11" customHeight="1" ht="12">
+      <c r="A38" s="21"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
+    </row>
+    <row r="39" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A39" s="17"/>
+      <c r="B39" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="26"/>
       <c r="D39" s="26"/>
       <c r="E39" s="26"/>
-      <c r="H39" s="25" t="str">
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
+    </row>
+    <row r="40" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+    </row>
+    <row r="41" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+    </row>
+    <row r="42" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="H42" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+    </row>
+    <row r="43" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="44" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="23"/>
+      <c r="J44" s="23"/>
+    </row>
+    <row r="45" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="46" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C46" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="H46" s="25" t="str">
         <f>C8</f>
         <v>Abraham Palayot Sanchez</v>
       </c>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-    </row>
-    <row r="40" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C40" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="H40" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-    </row>
-    <row r="41" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-    </row>
-    <row r="42" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="43" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A43" s="22"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="26"/>
+    </row>
+    <row r="47" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C47" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="H47" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="I47" s="26"/>
+      <c r="J47" s="26"/>
+    </row>
+    <row r="48" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H48" s="22"/>
+      <c r="I48" s="22"/>
+      <c r="J48" s="22"/>
+    </row>
+    <row r="49" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="50" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A50" s="22"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="F52" s="22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="E54" s="23"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="23"/>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="F56" s="22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="F57" s="22" t="s">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
@@ -1363,26 +1582,26 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="B26:J26"/>
-    <mergeCell ref="B27:J27"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="B29:J29"/>
-    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
     <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="H46:J46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="H47:J47"/>
+    <mergeCell ref="B33:J33"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="B38:J38"/>
+    <mergeCell ref="B39:J39"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -1395,7 +1614,28 @@
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I17:J20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I17:J27"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>14/07/2025</t>
+    <t>15/07/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>TI</t>
+    <t>sw</t>
   </si>
   <si>
     <t>Región:</t>
@@ -59,7 +59,7 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>BASE OPERATIVA</t>
+    <t>sws</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
@@ -192,12 +192,6 @@
   </si>
   <si>
     <t>Supervisor de Información Financiera</t>
-  </si>
-  <si>
-    <t>Ricardo</t>
-  </si>
-  <si>
-    <t>Supervisor</t>
   </si>
 </sst>
 </file>
@@ -864,7 +858,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -1548,26 +1542,6 @@
       <c r="C50" s="22"/>
       <c r="D50" s="22"/>
       <c r="E50" s="22"/>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="F52" s="22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
-      <c r="E54" s="23"/>
-      <c r="F54" s="23"/>
-      <c r="G54" s="23"/>
-    </row>
-    <row r="56" spans="1:11">
-      <c r="F56" s="22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
-      <c r="F57" s="22" t="s">
-        <v>60</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>15/07/2025</t>
+    <t>04/08/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>sw</t>
+    <t>x</t>
   </si>
   <si>
     <t>Región:</t>
@@ -59,9 +59,6 @@
     <t>Ubicación:</t>
   </si>
   <si>
-    <t>sws</t>
-  </si>
-  <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
   </si>
   <si>
@@ -92,12 +89,6 @@
     <t>Latitude 5520</t>
   </si>
   <si>
-    <t>1446MG00C698</t>
-  </si>
-  <si>
-    <t>Y8GS78BY8</t>
-  </si>
-  <si>
     <t>64W9FG3</t>
   </si>
   <si>
@@ -108,12 +99,6 @@
   </si>
   <si>
     <t>HP</t>
-  </si>
-  <si>
-    <t>LA65NM190</t>
-  </si>
-  <si>
-    <t>CN-0VT148-LOC00-18C-3AF4-A02</t>
   </si>
   <si>
     <t>HSTNN-DA40</t>
@@ -858,7 +843,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -997,7 +982,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
@@ -1006,7 +991,7 @@
     <row r="12" spans="1:11" customHeight="1" ht="15.75">
       <c r="A12" s="13"/>
       <c r="B12" s="38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
@@ -1055,24 +1040,24 @@
     <row r="16" spans="1:11" customHeight="1" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="D16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="E16" s="39" t="s">
         <v>18</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>19</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H16" s="40"/>
       <c r="I16" s="39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J16" s="40"/>
       <c r="K16" s="17"/>
@@ -1083,17 +1068,17 @@
         <v>1</v>
       </c>
       <c r="C17" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="E17" s="53" t="s">
         <v>23</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>24</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
@@ -1106,7 +1091,7 @@
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
       <c r="E18" s="51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="53"/>
       <c r="G18" s="53"/>
@@ -1121,17 +1106,17 @@
         <v>2</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F19" s="53"/>
       <c r="G19" s="53" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
@@ -1140,14 +1125,22 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="52"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="51" t="s">
-        <v>28</v>
+      <c r="B20" s="53">
+        <v>3</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="53" t="s">
+        <v>32</v>
       </c>
       <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
+      <c r="G20" s="53" t="s">
+        <v>33</v>
+      </c>
       <c r="H20" s="53"/>
       <c r="I20" s="53"/>
       <c r="J20" s="53"/>
@@ -1156,20 +1149,20 @@
     <row r="21" spans="1:11">
       <c r="A21" s="52"/>
       <c r="B21" s="53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="53" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H21" s="53"/>
       <c r="I21" s="53"/>
@@ -1178,22 +1171,14 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="52"/>
-      <c r="B22" s="53">
-        <v>4</v>
-      </c>
-      <c r="C22" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="53" t="s">
-        <v>33</v>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="51" t="s">
+        <v>37</v>
       </c>
       <c r="F22" s="53"/>
-      <c r="G22" s="53" t="s">
-        <v>34</v>
-      </c>
+      <c r="G22" s="53"/>
       <c r="H22" s="53"/>
       <c r="I22" s="53"/>
       <c r="J22" s="53"/>
@@ -1205,17 +1190,17 @@
         <v>5</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D23" s="53" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E23" s="53" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F23" s="53"/>
       <c r="G23" s="53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
@@ -1228,10 +1213,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D24" s="53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E24" s="53" t="s">
         <v>40</v>
@@ -1245,107 +1230,86 @@
       <c r="J24" s="53"/>
       <c r="K24" s="17"/>
     </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="52"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="51" t="s">
+    <row r="25" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A25" s="18"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="31"/>
+    </row>
+    <row r="26" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A26" s="18"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="31"/>
+    </row>
+    <row r="27" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+    </row>
+    <row r="28" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A28" s="19"/>
+      <c r="B28" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="53"/>
-      <c r="G25" s="53"/>
-      <c r="H25" s="53"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="17"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="52"/>
-      <c r="B26" s="53">
-        <v>7</v>
-      </c>
-      <c r="C26" s="53" t="s">
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+    </row>
+    <row r="29" spans="1:11" customHeight="1" ht="9">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A30" s="20"/>
+      <c r="B30" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="53" t="s">
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+    </row>
+    <row r="31" spans="1:11" customHeight="1" ht="15">
+      <c r="A31" s="20"/>
+      <c r="B31" s="27" t="s">
         <v>44</v>
-      </c>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="17"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="52"/>
-      <c r="B27" s="53">
-        <v>8</v>
-      </c>
-      <c r="C27" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="H27" s="53"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="17"/>
-    </row>
-    <row r="28" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A28" s="18"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="31"/>
-    </row>
-    <row r="29" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A29" s="18"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="31"/>
-    </row>
-    <row r="30" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-    </row>
-    <row r="31" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A31" s="19"/>
-      <c r="B31" s="33" t="s">
-        <v>47</v>
       </c>
       <c r="C31" s="26"/>
       <c r="D31" s="26"/>
@@ -1356,22 +1320,24 @@
       <c r="I31" s="26"/>
       <c r="J31" s="26"/>
     </row>
-    <row r="32" spans="1:11" customHeight="1" ht="9">
+    <row r="32" spans="1:11" customHeight="1" ht="15">
       <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-    </row>
-    <row r="33" spans="1:11" customHeight="1" ht="15.75">
+      <c r="B32" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+    </row>
+    <row r="33" spans="1:11" customHeight="1" ht="15">
       <c r="A33" s="20"/>
       <c r="B33" s="27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C33" s="26"/>
       <c r="D33" s="26"/>
@@ -1385,7 +1351,7 @@
     <row r="34" spans="1:11" customHeight="1" ht="15">
       <c r="A34" s="20"/>
       <c r="B34" s="27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
@@ -1396,11 +1362,9 @@
       <c r="I34" s="26"/>
       <c r="J34" s="26"/>
     </row>
-    <row r="35" spans="1:11" customHeight="1" ht="15">
-      <c r="A35" s="20"/>
-      <c r="B35" s="27" t="s">
-        <v>50</v>
-      </c>
+    <row r="35" spans="1:11" customHeight="1" ht="12">
+      <c r="A35" s="21"/>
+      <c r="B35" s="28"/>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
@@ -1410,10 +1374,10 @@
       <c r="I35" s="26"/>
       <c r="J35" s="26"/>
     </row>
-    <row r="36" spans="1:11" customHeight="1" ht="15">
-      <c r="A36" s="20"/>
-      <c r="B36" s="27" t="s">
-        <v>51</v>
+    <row r="36" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A36" s="17"/>
+      <c r="B36" s="29" t="s">
+        <v>48</v>
       </c>
       <c r="C36" s="26"/>
       <c r="D36" s="26"/>
@@ -1424,124 +1388,84 @@
       <c r="I36" s="26"/>
       <c r="J36" s="26"/>
     </row>
-    <row r="37" spans="1:11" customHeight="1" ht="15">
-      <c r="A37" s="20"/>
-      <c r="B37" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-    </row>
-    <row r="38" spans="1:11" customHeight="1" ht="12">
-      <c r="A38" s="21"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-    </row>
-    <row r="39" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A39" s="17"/>
-      <c r="B39" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" s="26"/>
+    <row r="37" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A37" s="22"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+    </row>
+    <row r="38" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+    </row>
+    <row r="39" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="25" t="s">
+        <v>49</v>
+      </c>
       <c r="D39" s="26"/>
       <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
+      <c r="H39" s="34" t="s">
+        <v>50</v>
+      </c>
       <c r="I39" s="26"/>
       <c r="J39" s="26"/>
     </row>
-    <row r="40" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A40" s="22"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-    </row>
+    <row r="40" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="41" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-    </row>
-    <row r="42" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="H42" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-    </row>
-    <row r="43" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="44" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="23"/>
-      <c r="J44" s="23"/>
-    </row>
-    <row r="45" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="46" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C46" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="H46" s="25" t="str">
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="23"/>
+    </row>
+    <row r="42" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="43" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C43" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="H43" s="25" t="str">
         <f>C8</f>
         <v>Abraham Palayot Sanchez</v>
       </c>
-      <c r="I46" s="26"/>
-      <c r="J46" s="26"/>
-    </row>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
+    </row>
+    <row r="44" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C44" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="H44" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="I44" s="26"/>
+      <c r="J44" s="26"/>
+    </row>
+    <row r="45" spans="1:11" customHeight="1" ht="15.75">
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="22"/>
+    </row>
+    <row r="46" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="47" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C47" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="H47" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="I47" s="26"/>
-      <c r="J47" s="26"/>
-    </row>
-    <row r="48" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H48" s="22"/>
-      <c r="I48" s="22"/>
-      <c r="J48" s="22"/>
-    </row>
-    <row r="49" spans="1:11" customHeight="1" ht="15.75"/>
-    <row r="50" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A50" s="22"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
+      <c r="A47" s="22"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -1556,26 +1480,26 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="B30:J30"/>
     <mergeCell ref="B31:J31"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="H46:J46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="H47:J47"/>
+    <mergeCell ref="B32:J32"/>
     <mergeCell ref="B33:J33"/>
     <mergeCell ref="B34:J34"/>
     <mergeCell ref="B35:J35"/>
     <mergeCell ref="B36:J36"/>
-    <mergeCell ref="B37:J37"/>
-    <mergeCell ref="B38:J38"/>
-    <mergeCell ref="B39:J39"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -1600,16 +1524,7 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I17:J27"/>
+    <mergeCell ref="I17:J24"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>04/08/2025</t>
+    <t>05/08/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>x</t>
+    <t>tr</t>
   </si>
   <si>
     <t>Región:</t>
@@ -87,6 +87,12 @@
   </si>
   <si>
     <t>Latitude 5520</t>
+  </si>
+  <si>
+    <t>1446MG00C698</t>
+  </si>
+  <si>
+    <t>Y8GS78BY8</t>
   </si>
   <si>
     <t>64W9FG3</t>
@@ -843,7 +849,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -1106,17 +1112,17 @@
         <v>2</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F19" s="53"/>
       <c r="G19" s="53" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
@@ -1125,22 +1131,14 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="52"/>
-      <c r="B20" s="53">
-        <v>3</v>
-      </c>
-      <c r="C20" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="53" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="53" t="s">
-        <v>32</v>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="51" t="s">
+        <v>27</v>
       </c>
       <c r="F20" s="53"/>
-      <c r="G20" s="53" t="s">
-        <v>33</v>
-      </c>
+      <c r="G20" s="53"/>
       <c r="H20" s="53"/>
       <c r="I20" s="53"/>
       <c r="J20" s="53"/>
@@ -1149,20 +1147,20 @@
     <row r="21" spans="1:11">
       <c r="A21" s="52"/>
       <c r="B21" s="53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="53" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H21" s="53"/>
       <c r="I21" s="53"/>
@@ -1171,14 +1169,22 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="52"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="51" t="s">
-        <v>37</v>
+      <c r="B22" s="53">
+        <v>4</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="53" t="s">
+        <v>34</v>
       </c>
       <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
+      <c r="G22" s="53" t="s">
+        <v>35</v>
+      </c>
       <c r="H22" s="53"/>
       <c r="I22" s="53"/>
       <c r="J22" s="53"/>
@@ -1190,17 +1196,17 @@
         <v>5</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D23" s="53" t="s">
         <v>22</v>
       </c>
       <c r="E23" s="53" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F23" s="53"/>
       <c r="G23" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
@@ -1209,93 +1215,105 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="52"/>
-      <c r="B24" s="53">
-        <v>6</v>
-      </c>
-      <c r="C24" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="53" t="s">
-        <v>40</v>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="51" t="s">
+        <v>39</v>
       </c>
       <c r="F24" s="53"/>
-      <c r="G24" s="53" t="s">
-        <v>41</v>
-      </c>
+      <c r="G24" s="53"/>
       <c r="H24" s="53"/>
       <c r="I24" s="53"/>
       <c r="J24" s="53"/>
       <c r="K24" s="17"/>
     </row>
-    <row r="25" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A25" s="18"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="31"/>
-    </row>
-    <row r="26" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A26" s="18"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="31"/>
+    <row r="25" spans="1:11">
+      <c r="A25" s="52"/>
+      <c r="B25" s="53">
+        <v>6</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="17"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="52"/>
+      <c r="B26" s="53">
+        <v>7</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="17"/>
     </row>
     <row r="27" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="31"/>
     </row>
     <row r="28" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A28" s="19"/>
-      <c r="B28" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-    </row>
-    <row r="29" spans="1:11" customHeight="1" ht="9">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="31"/>
+    </row>
+    <row r="29" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
     </row>
     <row r="30" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A30" s="20"/>
-      <c r="B30" s="27" t="s">
-        <v>43</v>
+      <c r="A30" s="19"/>
+      <c r="B30" s="33" t="s">
+        <v>44</v>
       </c>
       <c r="C30" s="26"/>
       <c r="D30" s="26"/>
@@ -1306,21 +1324,19 @@
       <c r="I30" s="26"/>
       <c r="J30" s="26"/>
     </row>
-    <row r="31" spans="1:11" customHeight="1" ht="15">
+    <row r="31" spans="1:11" customHeight="1" ht="9">
       <c r="A31" s="20"/>
-      <c r="B31" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-    </row>
-    <row r="32" spans="1:11" customHeight="1" ht="15">
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+    </row>
+    <row r="32" spans="1:11" customHeight="1" ht="15.75">
       <c r="A32" s="20"/>
       <c r="B32" s="27" t="s">
         <v>45</v>
@@ -1362,9 +1378,11 @@
       <c r="I34" s="26"/>
       <c r="J34" s="26"/>
     </row>
-    <row r="35" spans="1:11" customHeight="1" ht="12">
-      <c r="A35" s="21"/>
-      <c r="B35" s="28"/>
+    <row r="35" spans="1:11" customHeight="1" ht="15">
+      <c r="A35" s="20"/>
+      <c r="B35" s="27" t="s">
+        <v>48</v>
+      </c>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
       <c r="E35" s="26"/>
@@ -1374,10 +1392,10 @@
       <c r="I35" s="26"/>
       <c r="J35" s="26"/>
     </row>
-    <row r="36" spans="1:11" customHeight="1" ht="27.75">
-      <c r="A36" s="17"/>
-      <c r="B36" s="29" t="s">
-        <v>48</v>
+    <row r="36" spans="1:11" customHeight="1" ht="15">
+      <c r="A36" s="20"/>
+      <c r="B36" s="27" t="s">
+        <v>49</v>
       </c>
       <c r="C36" s="26"/>
       <c r="D36" s="26"/>
@@ -1388,84 +1406,110 @@
       <c r="I36" s="26"/>
       <c r="J36" s="26"/>
     </row>
-    <row r="37" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-    </row>
-    <row r="38" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
+    <row r="37" spans="1:11" customHeight="1" ht="12">
+      <c r="A37" s="21"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+    </row>
+    <row r="38" spans="1:11" customHeight="1" ht="27.75">
+      <c r="A38" s="17"/>
+      <c r="B38" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
     </row>
     <row r="39" spans="1:11" customHeight="1" ht="15.75">
       <c r="A39" s="22"/>
       <c r="B39" s="22"/>
-      <c r="C39" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="H39" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-    </row>
-    <row r="40" spans="1:11" customHeight="1" ht="15.75"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+    </row>
+    <row r="40" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+    </row>
     <row r="41" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
-      <c r="J41" s="23"/>
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="H41" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
     </row>
     <row r="42" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="43" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C43" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="H43" s="25" t="str">
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="23"/>
+    </row>
+    <row r="44" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="45" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C45" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="H45" s="25" t="str">
         <f>C8</f>
         <v>Abraham Palayot Sanchez</v>
       </c>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
-    </row>
-    <row r="44" spans="1:11" customHeight="1" ht="15.75">
-      <c r="C44" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="H44" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
-    </row>
-    <row r="45" spans="1:11" customHeight="1" ht="15.75">
-      <c r="H45" s="22"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="22"/>
-    </row>
-    <row r="46" spans="1:11" customHeight="1" ht="15.75"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+    </row>
+    <row r="46" spans="1:11" customHeight="1" ht="15.75">
+      <c r="C46" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="H46" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="I46" s="26"/>
+      <c r="J46" s="26"/>
+    </row>
     <row r="47" spans="1:11" customHeight="1" ht="15.75">
-      <c r="A47" s="22"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="22"/>
+    </row>
+    <row r="48" spans="1:11" customHeight="1" ht="15.75"/>
+    <row r="49" spans="1:11" customHeight="1" ht="15.75">
+      <c r="A49" s="22"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -1480,26 +1524,26 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B28:J28"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="H39:J39"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
     <mergeCell ref="B30:J30"/>
-    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="H46:J46"/>
     <mergeCell ref="B32:J32"/>
     <mergeCell ref="B33:J33"/>
     <mergeCell ref="B34:J34"/>
     <mergeCell ref="B35:J35"/>
     <mergeCell ref="B36:J36"/>
+    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="B38:J38"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="I17:J17"/>
@@ -1524,7 +1568,13 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I17:J24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I17:J26"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0" footer="0"/>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="57">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>05/08/2025</t>
+    <t>18/08/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>tr</t>
+    <t>io</t>
   </si>
   <si>
     <t>Región:</t>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>Ubicación:</t>
+  </si>
+  <si>
+    <t>oi</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
@@ -988,7 +991,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
@@ -997,7 +1000,7 @@
     <row r="12" spans="1:11" customHeight="1" ht="15.75">
       <c r="A12" s="13"/>
       <c r="B12" s="38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
@@ -1046,58 +1049,58 @@
     <row r="16" spans="1:11" customHeight="1" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H16" s="40"/>
       <c r="I16" s="39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J16" s="40"/>
       <c r="K16" s="17"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" customHeight="1" ht="15.75">
       <c r="A17" s="52"/>
       <c r="B17" s="53">
         <v>1</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17" s="53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="53" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
       <c r="J17" s="51"/>
       <c r="K17" s="17"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" customHeight="1" ht="15.75">
       <c r="A18" s="52"/>
       <c r="B18" s="53"/>
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
       <c r="E18" s="51" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="53"/>
       <c r="G18" s="53"/>
@@ -1106,36 +1109,36 @@
       <c r="J18" s="53"/>
       <c r="K18" s="17"/>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" customHeight="1" ht="15.75">
       <c r="A19" s="52"/>
       <c r="B19" s="53">
         <v>2</v>
       </c>
       <c r="C19" s="53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E19" s="53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F19" s="53"/>
       <c r="G19" s="53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
       <c r="J19" s="53"/>
       <c r="K19" s="17"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" customHeight="1" ht="15.75">
       <c r="A20" s="52"/>
       <c r="B20" s="53"/>
       <c r="C20" s="53"/>
       <c r="D20" s="53"/>
       <c r="E20" s="51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F20" s="53"/>
       <c r="G20" s="53"/>
@@ -1144,82 +1147,82 @@
       <c r="J20" s="53"/>
       <c r="K20" s="17"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" customHeight="1" ht="15.75">
       <c r="A21" s="52"/>
       <c r="B21" s="53">
         <v>3</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="53" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H21" s="53"/>
       <c r="I21" s="53"/>
       <c r="J21" s="53"/>
       <c r="K21" s="17"/>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" customHeight="1" ht="15.75">
       <c r="A22" s="52"/>
       <c r="B22" s="53">
         <v>4</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E22" s="53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F22" s="53"/>
       <c r="G22" s="53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H22" s="53"/>
       <c r="I22" s="53"/>
       <c r="J22" s="53"/>
       <c r="K22" s="17"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" customHeight="1" ht="15.75">
       <c r="A23" s="52"/>
       <c r="B23" s="53">
         <v>5</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D23" s="53" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E23" s="53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F23" s="53"/>
       <c r="G23" s="53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
       <c r="J23" s="53"/>
       <c r="K23" s="17"/>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" customHeight="1" ht="15.75">
       <c r="A24" s="52"/>
       <c r="B24" s="53"/>
       <c r="C24" s="53"/>
       <c r="D24" s="53"/>
       <c r="E24" s="51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F24" s="53"/>
       <c r="G24" s="53"/>
@@ -1228,46 +1231,46 @@
       <c r="J24" s="53"/>
       <c r="K24" s="17"/>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" customHeight="1" ht="15.75">
       <c r="A25" s="52"/>
       <c r="B25" s="53">
         <v>6</v>
       </c>
       <c r="C25" s="53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D25" s="53" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E25" s="53" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" s="53"/>
       <c r="G25" s="53" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H25" s="53"/>
       <c r="I25" s="53"/>
       <c r="J25" s="53"/>
       <c r="K25" s="17"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" customHeight="1" ht="15.75">
       <c r="A26" s="52"/>
       <c r="B26" s="53">
         <v>7</v>
       </c>
       <c r="C26" s="53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D26" s="53" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E26" s="53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="53" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H26" s="53"/>
       <c r="I26" s="53"/>
@@ -1313,7 +1316,7 @@
     <row r="30" spans="1:11" customHeight="1" ht="15.75">
       <c r="A30" s="19"/>
       <c r="B30" s="33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" s="26"/>
       <c r="D30" s="26"/>
@@ -1339,7 +1342,7 @@
     <row r="32" spans="1:11" customHeight="1" ht="15.75">
       <c r="A32" s="20"/>
       <c r="B32" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C32" s="26"/>
       <c r="D32" s="26"/>
@@ -1353,7 +1356,7 @@
     <row r="33" spans="1:11" customHeight="1" ht="15">
       <c r="A33" s="20"/>
       <c r="B33" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C33" s="26"/>
       <c r="D33" s="26"/>
@@ -1367,7 +1370,7 @@
     <row r="34" spans="1:11" customHeight="1" ht="15">
       <c r="A34" s="20"/>
       <c r="B34" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
@@ -1381,7 +1384,7 @@
     <row r="35" spans="1:11" customHeight="1" ht="15">
       <c r="A35" s="20"/>
       <c r="B35" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
@@ -1395,7 +1398,7 @@
     <row r="36" spans="1:11" customHeight="1" ht="15">
       <c r="A36" s="20"/>
       <c r="B36" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C36" s="26"/>
       <c r="D36" s="26"/>
@@ -1421,7 +1424,7 @@
     <row r="38" spans="1:11" customHeight="1" ht="27.75">
       <c r="A38" s="17"/>
       <c r="B38" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C38" s="26"/>
       <c r="D38" s="26"/>
@@ -1453,12 +1456,12 @@
       <c r="A41" s="22"/>
       <c r="B41" s="22"/>
       <c r="C41" s="25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="26"/>
       <c r="H41" s="34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I41" s="26"/>
       <c r="J41" s="26"/>
@@ -1475,7 +1478,7 @@
     <row r="44" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="45" spans="1:11" customHeight="1" ht="15.75">
       <c r="C45" s="25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D45" s="26"/>
       <c r="E45" s="26"/>
@@ -1488,12 +1491,12 @@
     </row>
     <row r="46" spans="1:11" customHeight="1" ht="15.75">
       <c r="C46" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D46" s="26"/>
       <c r="E46" s="26"/>
       <c r="H46" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I46" s="26"/>
       <c r="J46" s="26"/>

--- a/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
+++ b/database/controller_excel/Resguardo_Abraham_Palayot_Sanchez.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="56">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>18/08/2025</t>
+    <t>10/09/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>io</t>
+    <t>z</t>
   </si>
   <si>
     <t>Región:</t>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>Ubicación:</t>
-  </si>
-  <si>
-    <t>oi</t>
   </si>
   <si>
     <t>Por medio de la presente hago constar que la empresa: DIAVAZ me otorga las siguientes herramientas de trabajo para desempeñar mis funciones:</t>
@@ -991,7 +988,7 @@
         <v>13</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11" customHeight="1" ht="15.75">
@@ -1000,7 +997,7 @@
     <row r="12" spans="1:11" customHeight="1" ht="15.75">
       <c r="A12" s="13"/>
       <c r="B12" s="38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="26"/>
       <c r="D12" s="26"/>
@@ -1049,58 +1046,58 @@
     <row r="16" spans="1:11" customHeight="1" ht="15.75">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="D16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="E16" s="39" t="s">
         <v>18</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>19</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H16" s="40"/>
       <c r="I16" s="39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J16" s="40"/>
       <c r="K16" s="17"/>
     </row>
-    <row r="17" spans="1:11" customHeight="1" ht="15.75">
+    <row r="17" spans="1:11">
       <c r="A17" s="52"/>
       <c r="B17" s="53">
         <v>1</v>
       </c>
       <c r="C17" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="E17" s="53" t="s">
         <v>23</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>24</v>
       </c>
       <c r="F17" s="53"/>
       <c r="G17" s="53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
       <c r="J17" s="51"/>
       <c r="K17" s="17"/>
     </row>
-    <row r="18" spans="1:11" customHeight="1" ht="15.75">
+    <row r="18" spans="1:11">
       <c r="A18" s="52"/>
       <c r="B18" s="53"/>
       <c r="C18" s="53"/>
       <c r="D18" s="53"/>
       <c r="E18" s="51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="53"/>
       <c r="G18" s="53"/>
@@ -1109,36 +1106,36 @@
       <c r="J18" s="53"/>
       <c r="K18" s="17"/>
     </row>
-    <row r="19" spans="1:11" customHeight="1" ht="15.75">
+    <row r="19" spans="1:11">
       <c r="A19" s="52"/>
       <c r="B19" s="53">
         <v>2</v>
       </c>
       <c r="C19" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="53" t="s">
+      <c r="E19" s="53" t="s">
         <v>23</v>
-      </c>
-      <c r="E19" s="53" t="s">
-        <v>24</v>
       </c>
       <c r="F19" s="53"/>
       <c r="G19" s="53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
       <c r="J19" s="53"/>
       <c r="K19" s="17"/>
     </row>
-    <row r="20" spans="1:11" customHeight="1" ht="15.75">
+    <row r="20" spans="1:11">
       <c r="A20" s="52"/>
       <c r="B20" s="53"/>
       <c r="C20" s="53"/>
       <c r="D20" s="53"/>
       <c r="E20" s="51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F20" s="53"/>
       <c r="G20" s="53"/>
@@ -1147,82 +1144,82 @@
       <c r="J20" s="53"/>
       <c r="K20" s="17"/>
     </row>
-    <row r="21" spans="1:11" customHeight="1" ht="15.75">
+    <row r="21" spans="1:11">
       <c r="A21" s="52"/>
       <c r="B21" s="53">
         <v>3</v>
       </c>
       <c r="C21" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="53" t="s">
+      <c r="E21" s="53" t="s">
         <v>30</v>
-      </c>
-      <c r="E21" s="53" t="s">
-        <v>31</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H21" s="53"/>
       <c r="I21" s="53"/>
       <c r="J21" s="53"/>
       <c r="K21" s="17"/>
     </row>
-    <row r="22" spans="1:11" customHeight="1" ht="15.75">
+    <row r="22" spans="1:11">
       <c r="A22" s="52"/>
       <c r="B22" s="53">
         <v>4</v>
       </c>
       <c r="C22" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="53" t="s">
+      <c r="E22" s="53" t="s">
         <v>34</v>
-      </c>
-      <c r="E22" s="53" t="s">
-        <v>35</v>
       </c>
       <c r="F22" s="53"/>
       <c r="G22" s="53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H22" s="53"/>
       <c r="I22" s="53"/>
       <c r="J22" s="53"/>
       <c r="K22" s="17"/>
     </row>
-    <row r="23" spans="1:11" customHeight="1" ht="15.75">
+    <row r="23" spans="1:11">
       <c r="A23" s="52"/>
       <c r="B23" s="53">
         <v>5</v>
       </c>
       <c r="C23" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="53" t="s">
         <v>37</v>
-      </c>
-      <c r="D23" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="53" t="s">
-        <v>38</v>
       </c>
       <c r="F23" s="53"/>
       <c r="G23" s="53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
       <c r="J23" s="53"/>
       <c r="K23" s="17"/>
     </row>
-    <row r="24" spans="1:11" customHeight="1" ht="15.75">
+    <row r="24" spans="1:11">
       <c r="A24" s="52"/>
       <c r="B24" s="53"/>
       <c r="C24" s="53"/>
       <c r="D24" s="53"/>
       <c r="E24" s="51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F24" s="53"/>
       <c r="G24" s="53"/>
@@ -1231,46 +1228,46 @@
       <c r="J24" s="53"/>
       <c r="K24" s="17"/>
     </row>
-    <row r="25" spans="1:11" customHeight="1" ht="15.75">
+    <row r="25" spans="1:11">
       <c r="A25" s="52"/>
       <c r="B25" s="53">
         <v>6</v>
       </c>
       <c r="C25" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="53" t="s">
         <v>41</v>
-      </c>
-      <c r="D25" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="53" t="s">
-        <v>42</v>
       </c>
       <c r="F25" s="53"/>
       <c r="G25" s="53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H25" s="53"/>
       <c r="I25" s="53"/>
       <c r="J25" s="53"/>
       <c r="K25" s="17"/>
     </row>
-    <row r="26" spans="1:11" customHeight="1" ht="15.75">
+    <row r="26" spans="1:11">
       <c r="A26" s="52"/>
       <c r="B26" s="53">
         <v>7</v>
       </c>
       <c r="C26" s="53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" s="53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E26" s="53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F26" s="53"/>
       <c r="G26" s="53" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H26" s="53"/>
       <c r="I26" s="53"/>
@@ -1316,7 +1313,7 @@
     <row r="30" spans="1:11" customHeight="1" ht="15.75">
       <c r="A30" s="19"/>
       <c r="B30" s="33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" s="26"/>
       <c r="D30" s="26"/>
@@ -1342,7 +1339,7 @@
     <row r="32" spans="1:11" customHeight="1" ht="15.75">
       <c r="A32" s="20"/>
       <c r="B32" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" s="26"/>
       <c r="D32" s="26"/>
@@ -1356,7 +1353,7 @@
     <row r="33" spans="1:11" customHeight="1" ht="15">
       <c r="A33" s="20"/>
       <c r="B33" s="27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C33" s="26"/>
       <c r="D33" s="26"/>
@@ -1370,7 +1367,7 @@
     <row r="34" spans="1:11" customHeight="1" ht="15">
       <c r="A34" s="20"/>
       <c r="B34" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
@@ -1384,7 +1381,7 @@
     <row r="35" spans="1:11" customHeight="1" ht="15">
       <c r="A35" s="20"/>
       <c r="B35" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
@@ -1398,7 +1395,7 @@
     <row r="36" spans="1:11" customHeight="1" ht="15">
       <c r="A36" s="20"/>
       <c r="B36" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" s="26"/>
       <c r="D36" s="26"/>
@@ -1424,7 +1421,7 @@
     <row r="38" spans="1:11" customHeight="1" ht="27.75">
       <c r="A38" s="17"/>
       <c r="B38" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C38" s="26"/>
       <c r="D38" s="26"/>
@@ -1456,12 +1453,12 @@
       <c r="A41" s="22"/>
       <c r="B41" s="22"/>
       <c r="C41" s="25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="26"/>
       <c r="H41" s="34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I41" s="26"/>
       <c r="J41" s="26"/>
@@ -1478,7 +1475,7 @@
     <row r="44" spans="1:11" customHeight="1" ht="15.75"/>
     <row r="45" spans="1:11" customHeight="1" ht="15.75">
       <c r="C45" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D45" s="26"/>
       <c r="E45" s="26"/>
@@ -1491,12 +1488,12 @@
     </row>
     <row r="46" spans="1:11" customHeight="1" ht="15.75">
       <c r="C46" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D46" s="26"/>
       <c r="E46" s="26"/>
       <c r="H46" s="25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I46" s="26"/>
       <c r="J46" s="26"/>
